--- a/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
+++ b/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="446">
   <si>
     <t xml:space="preserve">Флип-модель: Kernweg 1, Хорн — сводка</t>
   </si>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Первый оплачиваемый месяц</t>
   </si>
   <si>
-    <t xml:space="preserve">Стоимость со сдачей: аренда / BAR</t>
+    <t xml:space="preserve">Стоимость сданного здания: аренда / доходность для инвестора</t>
   </si>
   <si>
     <t xml:space="preserve">Минус не закончившиеся каникулы</t>
@@ -177,522 +177,546 @@
     <t xml:space="preserve">Доходы: аренда за период и продажа</t>
   </si>
   <si>
+    <t xml:space="preserve">Все затраты: цена, налоги, ремонт, проценты, комиссии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заработок на каждые € 100 затрат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">прибыль до налога, делённая на все затраты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог на прибыль VPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль после налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Своих денег нужно сверх кредита (максимум)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сколько вложить из своего кармана в самый затратный момент проекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль на свои деньги до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль на свои деньги после налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность своих денег в пересчёте на год (IRR), до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">учитывает, сколько месяцев деньги заняты в проекте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность своих денег в пересчёте на год (IRR), после налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сколько вернётся на € 1 своих денег, после налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вложенное плюс чистая прибыль, делённые на вложенное</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Глазами покупателя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог на передачу, который платит покупатель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Его полная цена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Его доходность на все расходы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сравнить с 8,5–8,9 % у сданных объектов в Хорне</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потолок цены покупки (подбор моделью, базовые допущения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль 0 — дороже не покупать, продажа через 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ 10 на каждые € 100 затрат, продажа через 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ 15 на каждые € 100 затрат, продажа через 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль 0, продажа через 6 мес. (ст. 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ 10 на каждые € 100 затрат, продажа через 6 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность для инвестора, при которой прибыль = 0 (12 мес.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда, при которой прибыль = 0, € за м² (12 мес.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Значения подобраны Python-моделью; в Excel их можно перепроверить подбором параметра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Флип-модель: Kernweg 1, Хорн — допущения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Синие значения на жёлтом фоне можно менять: все листы пересчитаются. Суммы без НДС, евро.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена продавца (k.k.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funda in business, 16.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена покупки — наше предложение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−23 % к цене продавца; потолок без убытка — см. «Сводка»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь, м² VVO (полезная)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по объявлению: 2.016 м² VVO, 2.155 м² BVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог на передачу недвижимости</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ст. 14 WBR, нежилая недвижимость, 2026–2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка объекта: техника, грунт, право</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Консультант по покупке, % цены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подготовка к сдаче</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ремонт, € на м²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">покраска, свет, мелкий ремонт, разделение на два входа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ремонт, резерв</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НДС на ремонт (расход, пока аренда без НДС)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">при аренде с НДС возвращается</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяцев на ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сдача в аренду</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комиссия брокера, % годовой аренды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">рынок 10–16 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реклама и показы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Содержание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог OZB, страховка, ремонт: % цены в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энергия и охрана в простое, € на м² в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Финансирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кредит, доля цены покупки (LTV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">банк под пустое здание даёт 50–60 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euribor 3M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">euribor-rates.eu, 14.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маржа банка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оценка для кредита под пустое здание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комиссия банка, % кредита</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Брокер на продаже, % цены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Юрист и реклама продажи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля экономии покупателя по ст. 13 WBR, которую забираем в цене</t>
+  </si>
+  <si>
+    <t xml:space="preserve">только при продаже до 6 месяцев после нашей покупки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог на прибыль (VPB) 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставка до порога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KVK, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставка выше порога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Порог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставка кредита</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сценарии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Параметр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Активный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пессимистичный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Базовый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оптимистичный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ускоренный, 6 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда, множитель к оценке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность выхода (BAR k.k.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц начала аренды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Арендные каникулы, мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц продажи (передача у нотариуса)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Активный сценарий: 1 — пессимистичный, 2 — базовый, 3 — оптимистичный, 4 — ускоренный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денежный поток по месяцам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц 0 — передача у нотариуса и оплата; продажа — в конце месяца продажи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В работе (до продажи)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Покупка и расходы на сделку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энергия и охрана в простое</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сдача: брокер и реклама</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проценты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кредит: получен / погашен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поток до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накопленный поток</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Налог на прибыль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поток после налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оценка рыночной аренды по частям здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ставки — по предложениям в Хорне, Зваге, Энкхёйзене и Пюрмеренде на funda in business, 16.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Часть здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">м² VVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ за м² в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основание ставки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шоурум, первый этаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">витрина у въезда в Хорн 80, разрешена торговля; мелкие помещения в промзоне — € 85–100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шоурум и витрины, антресоль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">второй уровень шоурума, без отдельного входа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Офисы, два этажа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">офисы в деловых районах Хорна — € 120–150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кантина и подсобные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вспомогательные помещения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мастерские и склады, первый этаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">большие залы в Хорне и окрестностях — € 57–75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Склады и мастерские, второй этаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">склад на этаже без ворот</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итого</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда с учётом сценария</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К цене продавца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К цене покупки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сценарии и лестница цены покупки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рассчитано той же моделью; активный сценарий переключается на листе «Допущения»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Показатель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ускоренный, 6 месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доходность для инвестора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц продажи</t>
+  </si>
+  <si>
     <t xml:space="preserve">Все затраты</t>
   </si>
   <si>
-    <t xml:space="preserve">Прибыль до налога</t>
+    <t xml:space="preserve">Заработок на € 100 затрат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Своих денег нужно сверх кредита</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В пересчёте на год до налога (IRR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В пересчёте на год после налога (IRR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лестница цены покупки (базовые допущения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скидка к цене продавца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€ за м² VVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль, 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На € 100 затрат, 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В год, 12 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль, 6 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На € 100 затрат, 6 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В год, 6 мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чувствительность прибыли до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продажа через 12 месяцев; остальные допущения базовые</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль: цена покупки (строки) и доходность, которую требует инвестор (столбцы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена \ доходность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прибыль: аренда выше или ниже оценки (строки) и доходность для инвестора (столбцы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда \ доходность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц начала аренды (строки) × месяц продажи (столбцы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда \ продажа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля экономии покупателя по ст. 13, которую забираем (продажа через 6 мес.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">План Б: если быстро продать не получается</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Формулы от листов «Допущения», «Аренда» и «Сводка»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Держать сданным и рефинансировать</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расходы владельца, % аренды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">налог OZB владельца, страховка, ремонт, управление</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новый кредит, % стоимости со сдачей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чистый доход в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вложено всего</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чистая доходность на вложенное</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новый кредит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проценты в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитал после рефинансирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денежный поток в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Денежная доходность капитала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разделить на две части и продать пользователям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена продажи, € за м² VVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хорн 80: Electronplein 1 — € 922–999, De Marowijne 45 в Зваге — € 1.041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разделение: нотариус, кадастр, счётчики, противопожарная стена, второй вход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Срок, месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Брокер на продаже, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выручка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расходы на продажу двух частей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проценты за срок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Содержание и простой за срок</t>
   </si>
   <si>
     <t xml:space="preserve">Маржа на затраты</t>
   </si>
   <si>
-    <t xml:space="preserve">Налог на прибыль VPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прибыль после налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Собственный капитал (пик вложений)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">максимум накопленного отрицательного потока</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доходность капитала до налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доходность капитала после налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR годовая до налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR годовая после налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кратность капитала после налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Глазами покупателя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог на передачу, который платит покупатель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Его полная цена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Его валовая доходность на полную цену</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сравнить с 8,5–8,9 % у сданных объектов в Хорне (k.k.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Потолок цены покупки (подбор моделью, базовые допущения)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Без убытка, продажа через 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа 10 %, продажа через 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа 15 %, продажа через 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Без убытка, продажа через 6 мес. (ст. 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа 10 %, продажа через 6 мес. (ст. 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доходность выхода, при которой прибыль = 0 (12 мес.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда, при которой прибыль = 0, € за м² (12 мес.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Значения подобраны Python-моделью; в Excel их можно перепроверить подбором параметра.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Флип-модель: Kernweg 1, Хорн — допущения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Синие значения на жёлтом фоне можно менять: все листы пересчитаются. Суммы без НДС, евро.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена продавца (k.k.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">funda in business, 16.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена покупки — наше предложение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−23 % к цене продавца; потолок без убытка — см. «Сводка»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Площадь, м² VVO (полезная)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">по объявлению: 2.016 м² VVO, 2.155 м² BVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог на передачу недвижимости</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ст. 14 WBR, нежилая недвижимость, 2026–2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оценка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проверка объекта: техника, грунт, право</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Консультант по покупке, % цены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подготовка к сдаче</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ремонт, € на м²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">покраска, свет, мелкий ремонт, разделение на два входа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ремонт, резерв</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НДС на ремонт (расход, пока аренда без НДС)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">при аренде с НДС возвращается</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяцев на ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сдача в аренду</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Комиссия брокера, % годовой аренды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">рынок 10–16 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реклама и показы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Содержание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог OZB, страховка, ремонт: % цены в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Энергия и охрана в простое, € на м² в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Финансирование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кредит, доля цены покупки (LTV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">банк под пустое здание даёт 50–60 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euribor 3M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">euribor-rates.eu, 14.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа банка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">оценка для кредита под пустое здание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Комиссия банка, % кредита</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Брокер на продаже, % цены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Юрист и реклама продажи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля экономии покупателя по ст. 13 WBR, которую забираем в цене</t>
-  </si>
-  <si>
-    <t xml:space="preserve">только при продаже до 6 месяцев после нашей покупки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог на прибыль (VPB) 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставка до порога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KVK, 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставка выше порога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порог</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставка кредита</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сценарии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Параметр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Активный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пессимистичный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Базовый</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оптимистичный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ускоренный, 6 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда, множитель к оценке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доходность выхода (BAR k.k.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц начала аренды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Арендные каникулы, мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц продажи (передача у нотариуса)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Активный сценарий: 1 — пессимистичный, 2 — базовый, 3 — оптимистичный, 4 — ускоренный</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Денежный поток по месяцам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц 0 — передача у нотариуса и оплата; продажа — в конце месяца продажи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В работе (до продажи)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Покупка и расходы на сделку</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Энергия и охрана в простое</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сдача: брокер и реклама</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проценты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кредит: получен / погашен</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Поток до налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Накопленный поток</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Налог на прибыль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Поток после налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка рыночной аренды по частям здания</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ставки — по предложениям в Хорне, Зваге, Энкхёйзене и Пюрмеренде на funda in business, 16.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Часть здания</t>
-  </si>
-  <si>
-    <t xml:space="preserve">м² VVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€ за м² в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основание ставки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шоурум, первый этаж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">витрина у въезда в Хорн 80, разрешена торговля; мелкие помещения в промзоне — € 85–100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шоурум и витрины, антресоль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">второй уровень шоурума, без отдельного входа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Офисы, два этажа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">офисы в деловых районах Хорна — € 120–150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кантина и подсобные</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вспомогательные помещения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мастерские и склады, первый этаж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">большие залы в Хорне и окрестностях — € 57–75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Склады и мастерские, второй этаж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">склад на этаже без ворот</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Итого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда с учётом сценария</t>
-  </si>
-  <si>
-    <t xml:space="preserve">К цене продавца</t>
-  </si>
-  <si>
-    <t xml:space="preserve">К цене покупки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сценарии и лестница цены покупки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рассчитано той же моделью; активный сценарий переключается на листе «Допущения»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Показатель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ускоренный, 6 месяцев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доходность выхода</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц продажи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Собственный капитал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лестница цены покупки (базовые допущения)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Скидка к цене продавца</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€ за м² VVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прибыль, 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа, 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR, 12 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прибыль, 6 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Маржа, 6 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRR, 6 мес.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чувствительность прибыли до налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Продажа через 12 месяцев; остальные допущения базовые</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена покупки (строки) × доходность выхода (столбцы)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена \ BAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда к оценке (строки) × доходность выхода (столбцы)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда \ BAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц начала аренды (строки) × месяц продажи (столбцы)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аренда \ продажа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля экономии покупателя по ст. 13, которую забираем (продажа через 6 мес.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля</t>
-  </si>
-  <si>
-    <t xml:space="preserve">План Б: если быстро продать не получается</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Формулы от листов «Допущения», «Аренда» и «Сводка»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Держать сданным и рефинансировать</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расходы владельца, % аренды</t>
-  </si>
-  <si>
-    <t xml:space="preserve">налог OZB владельца, страховка, ремонт, управление</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новый кредит, % стоимости со сдачей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чистый доход в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вложено всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чистая доходность на вложенное</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новый кредит</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проценты в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Капитал после рефинансирования</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Денежный поток в год</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Денежная доходность капитала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разделить на две части и продать пользователям</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена продажи, € за м² VVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хорн 80: Electronplein 1 — € 922–999, De Marowijne 45 в Зваге — € 1.041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разделение: нотариус, кадастр, счётчики, противопожарная стена, второй вход</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Срок, месяцев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Брокер на продаже, %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выручка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расходы на продажу двух частей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проценты за срок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Содержание и простой за срок</t>
-  </si>
-  <si>
     <t xml:space="preserve">Сопоставимые объекты: Хорн и Западная Фрисландия</t>
   </si>
   <si>
@@ -1323,57 +1347,42 @@
     <t xml:space="preserve">https://www.fundainbusiness.nl/belegging/hoorn-nh/object-43660627-neutronweg-3/</t>
   </si>
   <si>
-    <t xml:space="preserve">Кандидаты на флип одной моделью: продажа через 12 месяцев</t>
+    <t xml:space="preserve">Другие здания по той же схеме: купить по цене продавца, сдать, продать через 12 месяцев</t>
   </si>
   <si>
     <t xml:space="preserve">Объект</t>
   </si>
   <si>
-    <t xml:space="preserve">Где</t>
-  </si>
-  <si>
     <t xml:space="preserve">Цена продавца</t>
   </si>
   <si>
-    <t xml:space="preserve">Аренда к цене</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAR выхода</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прибыль по цене продавца</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена для маржи 10 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Скидка</t>
+    <t xml:space="preserve">Аренда в год, оценка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итог по цене продавца</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сбить цену, чтобы выйти в ноль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сбить цену ради € 10 на € 100 затрат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цена для € 10 на € 100 затрат</t>
   </si>
   <si>
     <t xml:space="preserve">Kernweg 1, Хорн</t>
   </si>
   <si>
-    <t xml:space="preserve">Хорн 80, Agriport A7 и Хорн</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rijstenweg 4-6, Эйндховен</t>
   </si>
   <si>
-    <t xml:space="preserve">Де Хюрк, Эйндховен</t>
-  </si>
-  <si>
     <t xml:space="preserve">Electronplein 1 (часть), Хорн</t>
   </si>
   <si>
-    <t xml:space="preserve">Хорн 80</t>
-  </si>
-  <si>
     <t xml:space="preserve">Galvanistraat 122-126, Роттердам</t>
   </si>
   <si>
-    <t xml:space="preserve">Роттердам</t>
-  </si>
-  <si>
     <t xml:space="preserve">Industrieweg 99-B, Роттердам</t>
   </si>
   <si>
@@ -1383,13 +1392,7 @@
     <t xml:space="preserve">Karwijstraat 29-C и 29-D, Ньиве-Веннеп</t>
   </si>
   <si>
-    <t xml:space="preserve">рядом со Схипхолом</t>
-  </si>
-  <si>
     <t xml:space="preserve">Petroleumhavenweg 24, Амстердам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вестпорт, рядом со Слотердейком</t>
   </si>
   <si>
     <t xml:space="preserve">Источники и правила</t>
@@ -1445,10 +1448,10 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;€ &quot;#,##0;[RED]&quot;-€ &quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;€ &quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
-    <numFmt numFmtId="170" formatCode="&quot;€ &quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
     <numFmt numFmtId="171" formatCode="0%"/>
   </numFmts>
   <fonts count="13">
@@ -1644,19 +1647,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1672,7 +1671,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1680,7 +1679,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1688,11 +1687,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1721,6 +1720,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2232,13 +2235,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="9" t="n">
-        <f aca="false">profit/cost_total</f>
-        <v>0.0977026139276898</v>
+        <f aca="false">profit/cost_total*100</f>
+        <v>9.77026139276898</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" s="5" t="n">
         <f aca="false">IF(profit&lt;=0,0,MIN(profit,vpb_step)*vpb_low+MAX(0,profit-vpb_step)*vpb_high)</f>
@@ -2247,7 +2253,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="7" t="n">
         <f aca="false">profit-vpb</f>
@@ -2256,69 +2262,75 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="7" t="n">
         <f aca="false">-MIN('Денежный поток'!B16:Z16)</f>
         <v>822585.658333334</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B31" s="10" t="n">
         <f aca="false">profit/equity</f>
         <v>0.170427821586664</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B32" s="10" t="n">
         <f aca="false">(profit-vpb)/equity</f>
         <v>0.138046535485198</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" s="11" t="n">
         <f aca="false">(1+IRR('Денежный поток'!B15:Z15,0.01))^12-1</f>
         <v>0.176812251563086</v>
       </c>
+      <c r="C33" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B34" s="10" t="n">
         <f aca="false">(1+IRR('Денежный поток'!B18:Z18,0.01))^12-1</f>
         <v>0.143189239234856</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B35" s="9" t="n">
         <f aca="false">(equity+profit-vpb)/equity</f>
         <v>1.1380465354852</v>
       </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="n">
         <f aca="false">IF(sale_month&lt;=6,ovb*(sale_price-buy_price),ovb*sale_price)</f>
@@ -2327,7 +2339,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="n">
         <f aca="false">sale_price+buyer_ovb</f>
@@ -2336,84 +2348,84 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B39" s="12" t="n">
         <f aca="false">rent_eff/buyer_total</f>
         <v>0.0747282608695652</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>1271706</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="10" t="n">
         <f aca="false">B42/ask-1</f>
         <v>-0.149360535117057</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>1147398</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" s="10" t="n">
         <f aca="false">B43/ask-1</f>
         <v>-0.232509698996656</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>1093352</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" s="10" t="n">
         <f aca="false">B44/ask-1</f>
         <v>-0.268660869565217</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>1317315</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" s="10" t="n">
         <f aca="false">B45/ask-1</f>
         <v>-0.118852842809365</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>1183788</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" s="10" t="n">
         <f aca="false">B46/ask-1</f>
         <v>-0.20816856187291</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>0.0909824223174786</v>
@@ -2421,15 +2433,15 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B48" s="9" t="n">
         <v>56.6309741238001</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2459,318 +2471,318 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>1495000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>1150000</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <v>2016</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>0.104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="14" t="n">
         <v>3500</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B10" s="14" t="n">
         <v>7500</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="14" t="n">
         <v>3500</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="B12" s="16" t="n">
         <v>0.01</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>64</v>
+      <c r="A13" s="13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B14" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <v>2500</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="B16" s="16" t="n">
         <v>0.21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="B17" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>71</v>
+      <c r="A18" s="13" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="B19" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B20" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="C20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>75</v>
+      <c r="A21" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="18" t="n">
+        <v>79</v>
+      </c>
+      <c r="B22" s="17" t="n">
         <v>0.006</v>
       </c>
       <c r="C22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="B23" s="18" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>78</v>
+      <c r="A24" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="B25" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="B26" s="17" t="n">
         <v>0.02628</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="B27" s="17" t="n">
         <v>0.0275</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="B28" s="16" t="n">
         <v>0.01</v>
       </c>
       <c r="C28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="B30" s="17" t="n">
         <v>0.0125</v>
       </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="B31" s="14" t="n">
         <v>2500</v>
       </c>
       <c r="C31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B32" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>90</v>
+      <c r="A33" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="B34" s="16" t="n">
         <v>0.19</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="B35" s="17" t="n">
         <v>0.258</v>
       </c>
       <c r="C35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B36" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="B36" s="14" t="n">
         <v>200000</v>
       </c>
       <c r="C36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B37" s="12" t="n">
         <f aca="false">euribor+bank_margin</f>
@@ -2778,140 +2790,140 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>96</v>
+      <c r="A39" s="13" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40" s="20" t="s">
+      <c r="A40" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="B40" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="D40" s="19" t="s">
         <v>102</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="B41" s="20" t="n">
         <f aca="false">INDEX(D41:G41,scenario)</f>
         <v>1</v>
       </c>
-      <c r="D41" s="22" t="n">
+      <c r="D41" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="E41" s="22" t="n">
+      <c r="E41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="22" t="n">
+      <c r="F41" s="21" t="n">
         <v>1.1</v>
       </c>
-      <c r="G41" s="22" t="n">
+      <c r="G41" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B42" s="23" t="n">
+        <v>107</v>
+      </c>
+      <c r="B42" s="22" t="n">
         <f aca="false">INDEX(D42:G42,scenario)</f>
         <v>0.0825</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="17" t="n">
         <v>0.09</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="17" t="n">
         <v>0.0825</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="17" t="n">
         <v>0.0775</v>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="G42" s="17" t="n">
         <v>0.0825</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="24" t="n">
+        <v>108</v>
+      </c>
+      <c r="B43" s="23" t="n">
         <f aca="false">INDEX(D43:G43,scenario)</f>
         <v>5</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G43" s="15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B44" s="24" t="n">
+        <v>109</v>
+      </c>
+      <c r="B44" s="23" t="n">
         <f aca="false">INDEX(D44:G44,scenario)</f>
         <v>3</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="24" t="n">
+        <v>110</v>
+      </c>
+      <c r="B45" s="23" t="n">
         <f aca="false">INDEX(D45:G45,scenario)</f>
         <v>12</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="15" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="25" t="n">
+        <v>111</v>
+      </c>
+      <c r="B46" s="24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2940,97 +2952,97 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="20" t="n">
+        <v>114</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E3" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="G3" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="H3" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I3" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J3" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K3" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="L3" s="20" t="n">
+      <c r="L3" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="20" t="n">
+      <c r="M3" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="N3" s="20" t="n">
+      <c r="N3" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="O3" s="20" t="n">
+      <c r="O3" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="P3" s="20" t="n">
+      <c r="P3" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="Q3" s="20" t="n">
+      <c r="Q3" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="R3" s="20" t="n">
+      <c r="R3" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="S3" s="20" t="n">
+      <c r="S3" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="T3" s="20" t="n">
+      <c r="T3" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="U3" s="20" t="n">
+      <c r="U3" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="V3" s="20" t="n">
+      <c r="V3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="W3" s="20" t="n">
+      <c r="W3" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="X3" s="20" t="n">
+      <c r="X3" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="Y3" s="20" t="n">
+      <c r="Y3" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="Z3" s="20" t="n">
+      <c r="Z3" s="19" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B4" s="8" t="n">
         <f aca="false">IF(B$3&lt;=sale_month,1,0)</f>
@@ -3135,7 +3147,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">IF(B$3=0,-acq_total,0)</f>
@@ -3240,7 +3252,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">IF(AND(B$3&gt;=1,B$3&lt;=capex_months,B$3&lt;=sale_month),-capex_total/capex_months,0)</f>
@@ -3345,7 +3357,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">IF(AND(B$3&gt;=1,B$3&lt;=sale_month),-buy_price*holding_pct/12,0)</f>
@@ -3450,7 +3462,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">IF(AND(B$3&gt;=1,B$3&lt;lease_month,B$3&lt;=sale_month),-void_m2*area_vvo/12,0)</f>
@@ -3555,7 +3567,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">IF(AND(B$3=lease_month,B$3&lt;=sale_month),-(rent_eff*letting_fee+marketing),0)</f>
@@ -3660,7 +3672,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">IF(AND(B$3&gt;=1,B$3&gt;=first_paid,B$3&lt;=sale_month),rent_eff/12,0)</f>
@@ -3765,7 +3777,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">IF(AND(B$3&gt;=1,B$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
@@ -3870,7 +3882,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">IF(B$3=0,loan,0)-IF(B$3=sale_month,loan,0)</f>
@@ -4185,217 +4197,217 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" s="26" t="n">
+        <v>123</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <f aca="false">SUM(B5:B14)</f>
         <v>-726350</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="25" t="n">
         <f aca="false">SUM(C5:C14)</f>
         <v>-29562.0583333333</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">SUM(D5:D14)</f>
         <v>-29562.0583333333</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">SUM(E5:E14)</f>
         <v>-3655.95833333333</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">SUM(F5:F14)</f>
         <v>-3655.95833333333</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="25" t="n">
         <f aca="false">SUM(G5:G14)</f>
         <v>-23495.7083333333</v>
       </c>
-      <c r="H15" s="26" t="n">
+      <c r="H15" s="25" t="n">
         <f aca="false">SUM(H5:H14)</f>
         <v>-3151.95833333333</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="25" t="n">
         <f aca="false">SUM(I5:I14)</f>
         <v>-3151.95833333333</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="25" t="n">
         <f aca="false">SUM(J5:J14)</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="25" t="n">
         <f aca="false">SUM(K5:K14)</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="L15" s="26" t="n">
+      <c r="L15" s="25" t="n">
         <f aca="false">SUM(L5:L14)</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="M15" s="26" t="n">
+      <c r="M15" s="25" t="n">
         <f aca="false">SUM(M5:M14)</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="N15" s="26" t="n">
+      <c r="N15" s="25" t="n">
         <f aca="false">SUM(N5:N14)</f>
         <v>933509.973484848</v>
       </c>
-      <c r="O15" s="26" t="n">
+      <c r="O15" s="25" t="n">
         <f aca="false">SUM(O5:O14)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="26" t="n">
+      <c r="P15" s="25" t="n">
         <f aca="false">SUM(P5:P14)</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="26" t="n">
+      <c r="Q15" s="25" t="n">
         <f aca="false">SUM(Q5:Q14)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="26" t="n">
+      <c r="R15" s="25" t="n">
         <f aca="false">SUM(R5:R14)</f>
         <v>0</v>
       </c>
-      <c r="S15" s="26" t="n">
+      <c r="S15" s="25" t="n">
         <f aca="false">SUM(S5:S14)</f>
         <v>0</v>
       </c>
-      <c r="T15" s="26" t="n">
+      <c r="T15" s="25" t="n">
         <f aca="false">SUM(T5:T14)</f>
         <v>0</v>
       </c>
-      <c r="U15" s="26" t="n">
+      <c r="U15" s="25" t="n">
         <f aca="false">SUM(U5:U14)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="26" t="n">
+      <c r="V15" s="25" t="n">
         <f aca="false">SUM(V5:V14)</f>
         <v>0</v>
       </c>
-      <c r="W15" s="26" t="n">
+      <c r="W15" s="25" t="n">
         <f aca="false">SUM(W5:W14)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="26" t="n">
+      <c r="X15" s="25" t="n">
         <f aca="false">SUM(X5:X14)</f>
         <v>0</v>
       </c>
-      <c r="Y15" s="26" t="n">
+      <c r="Y15" s="25" t="n">
         <f aca="false">SUM(Y5:Y14)</f>
         <v>0</v>
       </c>
-      <c r="Z15" s="26" t="n">
+      <c r="Z15" s="25" t="n">
         <f aca="false">SUM(Z5:Z14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="26" t="n">
+        <v>124</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <f aca="false">B15</f>
         <v>-726350</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="25" t="n">
         <f aca="false">B16+C15</f>
         <v>-755912.058333333</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">C16+D15</f>
         <v>-785474.116666667</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">D16+E15</f>
         <v>-789130.075</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">E16+F15</f>
         <v>-792786.033333333</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="25" t="n">
         <f aca="false">F16+G15</f>
         <v>-816281.741666667</v>
       </c>
-      <c r="H16" s="26" t="n">
+      <c r="H16" s="25" t="n">
         <f aca="false">G16+H15</f>
         <v>-819433.7</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="25" t="n">
         <f aca="false">H16+I15</f>
         <v>-822585.658333334</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J16" s="25" t="n">
         <f aca="false">I16+J15</f>
         <v>-815268.866666667</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K16" s="25" t="n">
         <f aca="false">J16+K15</f>
         <v>-807952.075</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L16" s="25" t="n">
         <f aca="false">K16+L15</f>
         <v>-800635.283333334</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M16" s="25" t="n">
         <f aca="false">L16+M15</f>
         <v>-793318.491666667</v>
       </c>
-      <c r="N16" s="26" t="n">
+      <c r="N16" s="25" t="n">
         <f aca="false">M16+N15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="O16" s="26" t="n">
+      <c r="O16" s="25" t="n">
         <f aca="false">N16+O15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="P16" s="26" t="n">
+      <c r="P16" s="25" t="n">
         <f aca="false">O16+P15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="Q16" s="26" t="n">
+      <c r="Q16" s="25" t="n">
         <f aca="false">P16+Q15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="R16" s="26" t="n">
+      <c r="R16" s="25" t="n">
         <f aca="false">Q16+R15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="S16" s="26" t="n">
+      <c r="S16" s="25" t="n">
         <f aca="false">R16+S15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="T16" s="26" t="n">
+      <c r="T16" s="25" t="n">
         <f aca="false">S16+T15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="U16" s="26" t="n">
+      <c r="U16" s="25" t="n">
         <f aca="false">T16+U15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="V16" s="26" t="n">
+      <c r="V16" s="25" t="n">
         <f aca="false">U16+V15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="W16" s="26" t="n">
+      <c r="W16" s="25" t="n">
         <f aca="false">V16+W15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="X16" s="26" t="n">
+      <c r="X16" s="25" t="n">
         <f aca="false">W16+X15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="Y16" s="26" t="n">
+      <c r="Y16" s="25" t="n">
         <f aca="false">X16+Y15</f>
         <v>140191.481818181</v>
       </c>
-      <c r="Z16" s="26" t="n">
+      <c r="Z16" s="25" t="n">
         <f aca="false">Y16+Z15</f>
         <v>140191.481818181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B17" s="5" t="n">
         <f aca="false">IF(B$3=sale_month,-vpb,0)</f>
@@ -4500,105 +4512,105 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="26" t="n">
+        <v>126</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <f aca="false">B15+B17</f>
         <v>-726350</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="25" t="n">
         <f aca="false">C15+C17</f>
         <v>-29562.0583333333</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="25" t="n">
         <f aca="false">D15+D17</f>
         <v>-29562.0583333333</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <f aca="false">E15+E17</f>
         <v>-3655.95833333333</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <f aca="false">F15+F17</f>
         <v>-3655.95833333333</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="25" t="n">
         <f aca="false">G15+G17</f>
         <v>-23495.7083333333</v>
       </c>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="25" t="n">
         <f aca="false">H15+H17</f>
         <v>-3151.95833333333</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="25" t="n">
         <f aca="false">I15+I17</f>
         <v>-3151.95833333333</v>
       </c>
-      <c r="J18" s="26" t="n">
+      <c r="J18" s="25" t="n">
         <f aca="false">J15+J17</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="25" t="n">
         <f aca="false">K15+K17</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="L18" s="26" t="n">
+      <c r="L18" s="25" t="n">
         <f aca="false">L15+L17</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="M18" s="26" t="n">
+      <c r="M18" s="25" t="n">
         <f aca="false">M15+M17</f>
         <v>7316.79166666667</v>
       </c>
-      <c r="N18" s="26" t="n">
+      <c r="N18" s="25" t="n">
         <f aca="false">N15+N17</f>
         <v>906873.591939394</v>
       </c>
-      <c r="O18" s="26" t="n">
+      <c r="O18" s="25" t="n">
         <f aca="false">O15+O17</f>
         <v>0</v>
       </c>
-      <c r="P18" s="26" t="n">
+      <c r="P18" s="25" t="n">
         <f aca="false">P15+P17</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="26" t="n">
+      <c r="Q18" s="25" t="n">
         <f aca="false">Q15+Q17</f>
         <v>0</v>
       </c>
-      <c r="R18" s="26" t="n">
+      <c r="R18" s="25" t="n">
         <f aca="false">R15+R17</f>
         <v>0</v>
       </c>
-      <c r="S18" s="26" t="n">
+      <c r="S18" s="25" t="n">
         <f aca="false">S15+S17</f>
         <v>0</v>
       </c>
-      <c r="T18" s="26" t="n">
+      <c r="T18" s="25" t="n">
         <f aca="false">T15+T17</f>
         <v>0</v>
       </c>
-      <c r="U18" s="26" t="n">
+      <c r="U18" s="25" t="n">
         <f aca="false">U15+U17</f>
         <v>0</v>
       </c>
-      <c r="V18" s="26" t="n">
+      <c r="V18" s="25" t="n">
         <f aca="false">V15+V17</f>
         <v>0</v>
       </c>
-      <c r="W18" s="26" t="n">
+      <c r="W18" s="25" t="n">
         <f aca="false">W15+W17</f>
         <v>0</v>
       </c>
-      <c r="X18" s="26" t="n">
+      <c r="X18" s="25" t="n">
         <f aca="false">X15+X17</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="26" t="n">
+      <c r="Y18" s="25" t="n">
         <f aca="false">Y15+Y17</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="26" t="n">
+      <c r="Z18" s="25" t="n">
         <f aca="false">Z15+Z17</f>
         <v>0</v>
       </c>
@@ -4631,39 +4643,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="28" t="s">
+      <c r="A4" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>130</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>621</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>80</v>
       </c>
       <c r="D5" s="5" t="n">
@@ -4671,17 +4683,17 @@
         <v>49680</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>228</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="14" t="n">
         <v>45</v>
       </c>
       <c r="D6" s="5" t="n">
@@ -4689,17 +4701,17 @@
         <v>10260</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>121</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>110</v>
       </c>
       <c r="D7" s="5" t="n">
@@ -4707,17 +4719,17 @@
         <v>13310</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="14" t="n">
         <v>50</v>
       </c>
       <c r="D8" s="5" t="n">
@@ -4725,17 +4737,17 @@
         <v>2600</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>555</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="14" t="n">
         <v>62</v>
       </c>
       <c r="D9" s="5" t="n">
@@ -4743,17 +4755,17 @@
         <v>34410</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>439</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="14" t="n">
         <v>35</v>
       </c>
       <c r="D10" s="5" t="n">
@@ -4761,29 +4773,29 @@
         <v>15365</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" s="8" t="n">
         <f aca="false">SUM(B5:B10)</f>
         <v>2016</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">D11/B11</f>
         <v>62.3139880952381</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="25" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>125625</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">rent_base*rent_mult</f>
@@ -4792,7 +4804,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">rent_eff/ask</f>
@@ -4801,7 +4813,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D15" s="12" t="n">
         <f aca="false">rent_eff/buy_price</f>
@@ -4834,34 +4846,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>150</v>
+      <c r="A4" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>113062.5</v>
@@ -4878,7 +4890,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>0.09</v>
@@ -4895,7 +4907,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>8</v>
@@ -4912,7 +4924,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>15</v>
@@ -4946,7 +4958,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>1440632.075</v>
@@ -4980,24 +4992,24 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-0.101826536799828</v>
+        <v>-10.1826536799828</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.09770261392769</v>
+        <v>9.770261392769</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.284279599838898</v>
+        <v>28.4279599838899</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.128701483033222</v>
+        <v>12.8701483033222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>-146694.575</v>
@@ -5014,7 +5026,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>834821.116666667</v>
@@ -5031,94 +5043,94 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B15" s="10" t="n">
         <v>-0.175719770464998</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>0.138046535485198</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>0.38636357721352</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>0.181718556011389</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="B16" s="10" t="n">
         <v>-0.148860183152947</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <v>0.176812251563293</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>0.651009942053495</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>0.521319673310886</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="B17" s="10" t="n">
         <v>-0.148860183152947</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>0.143189239234859</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="10" t="n">
         <v>0.499947603789194</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>0.413709159362037</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="I21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>162</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>1495000</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="5" t="n">
@@ -5128,18 +5140,18 @@
         <v>-257210.568181818</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-0.140377204823742</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>-14.0377204823742</v>
+      </c>
+      <c r="F22" s="10" t="n">
         <v>-0.253591312223221</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>-193487.084848485</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>-0.107042738492903</v>
-      </c>
-      <c r="I22" s="9" t="n">
+        <v>-10.7042738492903</v>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>-0.349532835340184</v>
       </c>
     </row>
@@ -5147,7 +5159,7 @@
       <c r="A23" s="5" t="n">
         <v>1400000</v>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="10" t="n">
         <v>-0.0635451505016722</v>
       </c>
       <c r="C23" s="5" t="n">
@@ -5157,18 +5169,18 @@
         <v>-147781.018181818</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.0857769644013302</v>
-      </c>
-      <c r="F23" s="9" t="n">
+        <v>-8.57769644013301</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>-0.155026577758742</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>-90038.5145586296</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>-0.0529748846401385</v>
-      </c>
-      <c r="I23" s="9" t="n">
+        <v>-5.29748846401385</v>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>-0.182473541766482</v>
       </c>
     </row>
@@ -5176,7 +5188,7 @@
       <c r="A24" s="5" t="n">
         <v>1350000</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="10" t="n">
         <v>-0.096989966555184</v>
       </c>
       <c r="C24" s="5" t="n">
@@ -5186,18 +5198,18 @@
         <v>-90186.5181818181</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-0.0541576999150437</v>
-      </c>
-      <c r="F24" s="9" t="n">
+        <v>-5.41576999150437</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>-0.0979045459235878</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>-35591.8986166008</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>-0.0216648121664762</v>
-      </c>
-      <c r="I24" s="9" t="n">
+        <v>-2.16648121664762</v>
+      </c>
+      <c r="I24" s="10" t="n">
         <v>-0.0768782527626826</v>
       </c>
     </row>
@@ -5205,7 +5217,7 @@
       <c r="A25" s="5" t="n">
         <v>1300000</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="10" t="n">
         <v>-0.130434782608696</v>
       </c>
       <c r="C25" s="5" t="n">
@@ -5215,18 +5227,18 @@
         <v>-32592.0181818181</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>-0.020272916247044</v>
-      </c>
-      <c r="F25" s="9" t="n">
+        <v>-2.0272916247044</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>-0.0366580069387602</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>18854.7173254283</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.011887905897274</v>
-      </c>
-      <c r="I25" s="9" t="n">
+        <v>1.1887905897274</v>
+      </c>
+      <c r="I25" s="10" t="n">
         <v>0.0435119412078031</v>
       </c>
     </row>
@@ -5234,7 +5246,7 @@
       <c r="A26" s="5" t="n">
         <v>1250000</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="10" t="n">
         <v>-0.163879598662207</v>
       </c>
       <c r="C26" s="5" t="n">
@@ -5244,18 +5256,18 @@
         <v>25002.4818181819</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0161299201669614</v>
-      </c>
-      <c r="F26" s="9" t="n">
+        <v>1.61299201669614</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>0.0291741528367133</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>73301.3332674571</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.0479331702241912</v>
-      </c>
-      <c r="I26" s="9" t="n">
+        <v>4.79331702241912</v>
+      </c>
+      <c r="I26" s="10" t="n">
         <v>0.18120532097497</v>
       </c>
     </row>
@@ -5263,7 +5275,7 @@
       <c r="A27" s="5" t="n">
         <v>1200000</v>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="10" t="n">
         <v>-0.197324414715719</v>
       </c>
       <c r="C27" s="5" t="n">
@@ -5273,47 +5285,47 @@
         <v>82596.9818181819</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>0.0553423239226799</v>
-      </c>
-      <c r="F27" s="9" t="n">
+        <v>5.53423239226799</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>0.100124646517263</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>127747.949209486</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.0867594427707245</v>
-      </c>
-      <c r="I27" s="9" t="n">
+        <v>8.67594427707244</v>
+      </c>
+      <c r="I27" s="10" t="n">
         <v>0.339239713206038</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="29" t="n">
+      <c r="A28" s="28" t="n">
         <v>1150000</v>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="29" t="n">
         <v>-0.230769230769231</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="28" t="n">
         <v>570.436507936508</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="28" t="n">
         <v>140191.481818182</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>0.09770261392769</v>
-      </c>
-      <c r="F28" s="30" t="n">
+        <v>9.770261392769</v>
+      </c>
+      <c r="F28" s="29" t="n">
         <v>0.176812251563293</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="28" t="n">
         <v>182194.565151515</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>0.128701483033222</v>
-      </c>
-      <c r="I28" s="30" t="n">
+        <v>12.8701483033222</v>
+      </c>
+      <c r="I28" s="29" t="n">
         <v>0.521319673310886</v>
       </c>
     </row>
@@ -5321,7 +5333,7 @@
       <c r="A29" s="5" t="n">
         <v>1100000</v>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="10" t="n">
         <v>-0.264214046822743</v>
       </c>
       <c r="C29" s="5" t="n">
@@ -5331,18 +5343,18 @@
         <v>197785.981818182</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>0.143605699578085</v>
-      </c>
-      <c r="F29" s="9" t="n">
+        <v>14.3605699578085</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>0.259959934412725</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>236641.181093544</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.17415002463882</v>
-      </c>
-      <c r="I29" s="9" t="n">
+        <v>17.415002463882</v>
+      </c>
+      <c r="I29" s="10" t="n">
         <v>0.731996530866204</v>
       </c>
     </row>
@@ -5371,22 +5383,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>166</v>
+      <c r="A5" s="19" t="s">
+        <v>173</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>0.075</v>
@@ -5411,7 +5423,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="25" t="n">
         <v>1100000</v>
       </c>
       <c r="B6" s="5" t="n">
@@ -5437,7 +5449,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="25" t="n">
         <v>1150000</v>
       </c>
       <c r="B7" s="5" t="n">
@@ -5463,7 +5475,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="25" t="n">
         <v>1200000</v>
       </c>
       <c r="B8" s="5" t="n">
@@ -5489,7 +5501,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="25" t="n">
         <v>1250000</v>
       </c>
       <c r="B9" s="5" t="n">
@@ -5515,7 +5527,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="25" t="n">
         <v>1300000</v>
       </c>
       <c r="B10" s="5" t="n">
@@ -5541,7 +5553,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="25" t="n">
         <v>1400000</v>
       </c>
       <c r="B11" s="5" t="n">
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="25" t="n">
         <v>1495000</v>
       </c>
       <c r="B12" s="5" t="n">
@@ -5594,12 +5606,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>168</v>
+      <c r="A16" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="B16" s="31" t="n">
         <v>0.075</v>
@@ -5807,12 +5819,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
-        <v>170</v>
+      <c r="A27" s="19" t="s">
+        <v>177</v>
       </c>
       <c r="B27" s="33" t="n">
         <v>6</v>
@@ -5831,7 +5843,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="23" t="n">
         <v>3</v>
       </c>
       <c r="B28" s="5" t="n">
@@ -5851,7 +5863,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="23" t="n">
         <v>5</v>
       </c>
       <c r="B29" s="5" t="n">
@@ -5871,7 +5883,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="n">
+      <c r="A30" s="23" t="n">
         <v>7</v>
       </c>
       <c r="B30" s="5"/>
@@ -5889,7 +5901,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="n">
+      <c r="A31" s="23" t="n">
         <v>9</v>
       </c>
       <c r="B31" s="5"/>
@@ -5906,12 +5918,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B35" s="34" t="n">
         <v>0</v>
@@ -6011,42 +6023,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="17" t="n">
+        <v>183</v>
+      </c>
+      <c r="B5" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="17" t="n">
+        <v>185</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>0.55</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">rent_eff*(1-hold_opex)</f>
@@ -6056,7 +6068,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">acq_total+capex_total+rent_eff*letting_fee+marketing</f>
@@ -6066,7 +6078,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">hold_noi/hold_invested</f>
@@ -6076,7 +6088,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">refi_ltv*value_let</f>
@@ -6086,7 +6098,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">hold_loan*loan_rate</f>
@@ -6096,7 +6108,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">hold_invested-hold_loan</f>
@@ -6106,7 +6118,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">hold_noi-hold_int</f>
@@ -6116,9 +6128,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="B14" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="B14" s="10" t="n">
         <f aca="false">hold_cash/hold_eq</f>
         <v>0.12104553130427</v>
       </c>
@@ -6126,52 +6138,52 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" s="15" t="n">
+        <v>195</v>
+      </c>
+      <c r="B16" s="14" t="n">
         <v>850</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="15" t="n">
+        <v>197</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <v>90000</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="16" t="n">
+        <v>198</v>
+      </c>
+      <c r="B18" s="15" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="17" t="n">
+        <v>199</v>
+      </c>
+      <c r="B19" s="16" t="n">
         <v>0.02</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">split_pm2*area_vvo</f>
@@ -6181,7 +6193,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B21" s="5" t="n">
         <f aca="false">split_gross*split_fee+2*5000</f>
@@ -6191,7 +6203,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B22" s="5" t="n">
         <f aca="false">loan*loan_rate*split_months/12</f>
@@ -6201,7 +6213,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B23" s="5" t="n">
         <f aca="false">(buy_price*holding_pct+void_m2*area_vvo)*split_months/12</f>
@@ -6211,7 +6223,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="B24" s="5" t="n">
         <f aca="false">acq_total+capex_total+split_cost+split_int+split_hold+split_sale_cost</f>
@@ -6231,9 +6243,9 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="9" t="n">
+        <v>204</v>
+      </c>
+      <c r="B26" s="10" t="n">
         <f aca="false">(split_gross-split_total)/split_total</f>
         <v>0.124414035503448</v>
       </c>
@@ -6270,54 +6282,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="I5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>208</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>11195</v>
@@ -6329,24 +6341,24 @@
         <v>509</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1737</v>
@@ -6358,24 +6370,24 @@
         <v>518</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>11289</v>
@@ -6387,24 +6399,24 @@
         <v>576</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>4220</v>
@@ -6416,24 +6428,24 @@
         <v>662</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>2155</v>
@@ -6445,24 +6457,24 @@
         <v>694</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>694</v>
@@ -6474,24 +6486,24 @@
         <v>829</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>4500</v>
@@ -6503,24 +6515,24 @@
         <v>833</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>1625</v>
@@ -6532,24 +6544,24 @@
         <v>922</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>936</v>
@@ -6561,24 +6573,24 @@
         <v>935</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>1100</v>
@@ -6590,24 +6602,24 @@
         <v>999</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>11976</v>
@@ -6619,24 +6631,24 @@
         <v>1002</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>2258</v>
@@ -6648,24 +6660,24 @@
         <v>1041</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>3000</v>
@@ -6677,24 +6689,24 @@
         <v>1083</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>528</v>
@@ -6706,24 +6718,24 @@
         <v>1127</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>1628</v>
@@ -6735,24 +6747,24 @@
         <v>1161</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>462</v>
@@ -6764,24 +6776,24 @@
         <v>1180</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>471</v>
@@ -6793,24 +6805,24 @@
         <v>1258</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>446</v>
@@ -6822,24 +6834,24 @@
         <v>1289</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>869</v>
@@ -6851,24 +6863,24 @@
         <v>1375</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>563</v>
@@ -6880,24 +6892,24 @@
         <v>1465</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>400</v>
@@ -6909,24 +6921,24 @@
         <v>1480</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G26" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>271</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>1248</v>
@@ -6938,24 +6950,24 @@
         <v>1482</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>669</v>
@@ -6967,24 +6979,24 @@
         <v>1487</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>635</v>
@@ -6996,24 +7008,24 @@
         <v>1535</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>900</v>
@@ -7025,24 +7037,24 @@
         <v>1556</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>271</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>725</v>
@@ -7054,24 +7066,24 @@
         <v>1586</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>1205</v>
@@ -7083,24 +7095,24 @@
         <v>1618</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>774</v>
@@ -7112,24 +7124,24 @@
         <v>1738</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>762</v>
@@ -7141,24 +7153,24 @@
         <v>1739</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>271</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>460</v>
@@ -7170,1000 +7182,1000 @@
         <v>1739</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="I38" s="20" t="s">
+      <c r="A38" s="19" t="s">
         <v>208</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>12137</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="9" t="n">
         <v>49.4</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>599567.8</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>8583</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="9" t="n">
         <v>87.4</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>750154.2</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>5180</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="9" t="n">
         <v>56.8</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>294224</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>4676</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="9" t="n">
         <v>61.6</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>288041.6</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H42" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>2900</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="9" t="n">
         <v>60</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>174000</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H43" s="35" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>2710</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="9" t="n">
         <v>75.3</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>204063</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>2695</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="9" t="n">
         <v>70.1</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>188919.5</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>1776</v>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="9" t="n">
         <v>64.2</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>114019.2</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H46" s="35" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>1713</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="9" t="n">
         <v>57.4</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>98326.2</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H47" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1485</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="9" t="n">
         <v>75.1</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>111523.5</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="H48" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>1413</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="9" t="n">
         <v>78.6</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>111061.8</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="H49" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>1308</v>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="9" t="n">
         <v>82.6</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>108040.8</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H50" s="35" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>1278</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="9" t="n">
         <v>56.8</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>72590.4</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="H51" s="35" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="B52" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>271</v>
       </c>
       <c r="C52" s="8" t="n">
         <v>1248</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="9" t="n">
         <v>118.2</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>147513.6</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H52" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C53" s="8" t="n">
         <v>976</v>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="9" t="n">
         <v>153.7</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>150011.2</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="H53" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C54" s="8" t="n">
         <v>850</v>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="9" t="n">
         <v>84.7</v>
       </c>
       <c r="E54" s="5" t="n">
         <v>71995</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>762</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="9" t="n">
         <v>109.4</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>83362.8</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C56" s="8" t="n">
         <v>531</v>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="9" t="n">
         <v>58.2</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>30904.2</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="H56" s="35" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>482</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="9" t="n">
         <v>114.1</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>54996.2</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H57" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I57" s="36" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C58" s="8" t="n">
         <v>450</v>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="9" t="n">
         <v>144.4</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>64980</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H58" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>438</v>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="9" t="n">
         <v>99</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>43362</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H59" s="35" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="I59" s="36" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C60" s="8" t="n">
         <v>366</v>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="9" t="n">
         <v>94.9</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>34733.4</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H60" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I60" s="36" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>365</v>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="9" t="n">
         <v>70.7</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>25805.5</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="H61" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I61" s="36" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C62" s="8" t="n">
         <v>344</v>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="9" t="n">
         <v>99.4</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>34193.6</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C63" s="8" t="n">
         <v>342</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="9" t="n">
         <v>82.5</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>28215</v>
       </c>
       <c r="F63" s="35" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="H63" s="35" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="I63" s="36" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C64" s="8" t="n">
         <v>336</v>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="9" t="n">
         <v>64.1</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>21537.6</v>
       </c>
       <c r="F64" s="35" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H64" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I64" s="36" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C65" s="8" t="n">
         <v>335</v>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="9" t="n">
         <v>95.5</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>31992.5</v>
       </c>
       <c r="F65" s="35" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I65" s="36" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C66" s="8" t="n">
         <v>333</v>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="9" t="n">
         <v>84.7</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>28205.1</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H66" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>330</v>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="9" t="n">
         <v>75.8</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>25014</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H67" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C68" s="8" t="n">
         <v>325</v>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="9" t="n">
         <v>83.1</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>27007.5</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H68" s="35" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C69" s="8" t="n">
         <v>311</v>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="9" t="n">
         <v>192.9</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>59991.9</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C70" s="8" t="n">
         <v>310</v>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="9" t="n">
         <v>97.5</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>30225</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="H70" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C71" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="9" t="n">
         <v>112.6</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>34230.4</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C72" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="9" t="n">
         <v>108</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>32400</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H72" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C73" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="9" t="n">
         <v>78</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>23400</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="H73" s="35" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I73" s="36" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C76" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E76" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="G76" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="H76" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="I76" s="20" t="s">
+      <c r="A76" s="19" t="s">
         <v>208</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C77" s="8" t="n">
         <v>188</v>
@@ -8178,21 +8190,21 @@
         <v>0.0833</v>
       </c>
       <c r="G77" s="35" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="H77" s="35" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="I77" s="36" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>583</v>
@@ -8207,21 +8219,21 @@
         <v>0.0889</v>
       </c>
       <c r="G78" s="35" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="H78" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I78" s="36" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>190</v>
@@ -8236,21 +8248,21 @@
         <v>0.0935</v>
       </c>
       <c r="G79" s="35" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H79" s="35" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>2117</v>
@@ -8265,279 +8277,252 @@
         <v>0.0855</v>
       </c>
       <c r="G80" s="35" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="H80" s="35" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="B83" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="D83" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E83" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="G83" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="H83" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="I83" s="20" t="s">
-        <v>415</v>
+      <c r="A83" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="G83" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="H83" s="19" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="B84" s="0" t="s">
-        <v>417</v>
+        <v>423</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>1495000</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>1495000</v>
-      </c>
-      <c r="D84" s="5" t="n">
         <v>125625</v>
       </c>
-      <c r="E84" s="12" t="n">
-        <v>0.0840301003344482</v>
-      </c>
-      <c r="F84" s="12" t="n">
+      <c r="D84" s="12" t="n">
         <v>0.0825</v>
       </c>
-      <c r="G84" s="5" t="n">
+      <c r="E84" s="5" t="n">
         <v>-257210.568181818</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>0.149360792087094</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>0.232509452314799</v>
       </c>
       <c r="H84" s="5" t="n">
         <v>1147398.36878938</v>
       </c>
-      <c r="I84" s="9" t="n">
-        <v>-0.232509452314799</v>
-      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="B85" s="0" t="s">
-        <v>419</v>
+        <v>424</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>1795000</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1795000</v>
-      </c>
-      <c r="D85" s="5" t="n">
         <v>135875</v>
       </c>
-      <c r="E85" s="12" t="n">
-        <v>0.0756963788300836</v>
-      </c>
-      <c r="F85" s="12" t="n">
+      <c r="D85" s="12" t="n">
         <v>0.0775</v>
       </c>
-      <c r="G85" s="5" t="n">
+      <c r="E85" s="5" t="n">
         <v>-371897.732795699</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>0.179865583050465</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>0.259439755349203</v>
       </c>
       <c r="H85" s="5" t="n">
         <v>1329305.63914818</v>
       </c>
-      <c r="I85" s="9" t="n">
-        <v>-0.259439755349203</v>
-      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>420</v>
-      </c>
-      <c r="B86" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>1099000</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1099000</v>
-      </c>
-      <c r="D86" s="5" t="n">
         <v>71500</v>
       </c>
-      <c r="E86" s="12" t="n">
-        <v>0.0650591446769791</v>
-      </c>
-      <c r="F86" s="12" t="n">
+      <c r="D86" s="12" t="n">
         <v>0.0825</v>
       </c>
-      <c r="G86" s="5" t="n">
+      <c r="E86" s="5" t="n">
         <v>-440272.11</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>0.347786303431009</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>0.412163005278568</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>646032.857198854</v>
       </c>
-      <c r="I86" s="9" t="n">
-        <v>-0.412163005278568</v>
-      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="B87" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>1125000</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1125000</v>
-      </c>
-      <c r="D87" s="5" t="n">
         <v>78500</v>
       </c>
-      <c r="E87" s="12" t="n">
-        <v>0.0697777777777778</v>
-      </c>
-      <c r="F87" s="12" t="n">
+      <c r="D87" s="12" t="n">
         <v>0.075</v>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="E87" s="5" t="n">
         <v>-280423.783333333</v>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>0.216397038940511</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>0.292118003808877</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>796367.245715013</v>
       </c>
-      <c r="I87" s="9" t="n">
-        <v>-0.292118003808877</v>
-      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>424</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>495000</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>495000</v>
-      </c>
-      <c r="D88" s="5" t="n">
         <v>35190</v>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>0.0710909090909091</v>
-      </c>
-      <c r="F88" s="12" t="n">
+      <c r="D88" s="12" t="n">
         <v>0.075</v>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="E88" s="5" t="n">
         <v>-126702.75</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>0.222213190074705</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0.299359129672788</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>346817.23081197</v>
       </c>
-      <c r="I88" s="9" t="n">
-        <v>-0.299359129672788</v>
-      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="B89" s="0" t="s">
-        <v>423</v>
+        <v>428</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>390000</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>390000</v>
-      </c>
-      <c r="D89" s="5" t="n">
         <v>28000</v>
       </c>
-      <c r="E89" s="12" t="n">
-        <v>0.0717948717948718</v>
-      </c>
-      <c r="F89" s="12" t="n">
+      <c r="D89" s="12" t="n">
         <v>0.0775</v>
       </c>
-      <c r="G89" s="5" t="n">
+      <c r="E89" s="5" t="n">
         <v>-114711.239784946</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>0.255346764069455</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>0.33081956193202</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>260980.370846512</v>
       </c>
-      <c r="I89" s="9" t="n">
-        <v>-0.33081956193202</v>
-      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>426</v>
-      </c>
-      <c r="B90" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>825000</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>825000</v>
-      </c>
-      <c r="D90" s="5" t="n">
         <v>65100</v>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>0.0789090909090909</v>
-      </c>
-      <c r="F90" s="12" t="n">
+      <c r="D90" s="12" t="n">
         <v>0.0725</v>
       </c>
-      <c r="G90" s="5" t="n">
+      <c r="E90" s="5" t="n">
         <v>-83391.3534482757</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>0.0877518065285335</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>0.176245108193014</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>679597.785740763</v>
       </c>
-      <c r="I90" s="9" t="n">
-        <v>-0.176245108193014</v>
-      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="B91" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>550000</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>550000</v>
-      </c>
-      <c r="D91" s="5" t="n">
         <v>38920</v>
       </c>
-      <c r="E91" s="12" t="n">
-        <v>0.0707636363636364</v>
-      </c>
-      <c r="F91" s="12" t="n">
+      <c r="D91" s="12" t="n">
         <v>0.0725</v>
       </c>
-      <c r="G91" s="5" t="n">
+      <c r="E91" s="5" t="n">
         <v>-121574.191954023</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>0.191896783000939</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>0.271255292235537</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>400809.589270455</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>-0.271255292235537</v>
       </c>
     </row>
   </sheetData>
@@ -8636,79 +8621,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
+++ b/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
@@ -100,12 +100,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="445">
   <si>
     <t xml:space="preserve">Флип-модель: Kernweg 1, Хорн — сводка</t>
   </si>
   <si>
-    <t xml:space="preserve">Купить пустым → сдать → продать сданным инвестору. Все цифры — формулы от листов «Допущения» и «Аренда».</t>
+    <t xml:space="preserve">Купить пустым за свои средства → сдать → продать сданным инвестору. Все цифры — формулы от листов «Допущения» и «Аренда».</t>
   </si>
   <si>
     <t xml:space="preserve">Покупка</t>
@@ -177,7 +177,7 @@
     <t xml:space="preserve">Доходы: аренда за период и продажа</t>
   </si>
   <si>
-    <t xml:space="preserve">Все затраты: цена, налоги, ремонт, проценты, комиссии</t>
+    <t xml:space="preserve">Все затраты: цена, налоги, ремонт, комиссии</t>
   </si>
   <si>
     <t xml:space="preserve">Прибыль до налога</t>
@@ -195,10 +195,10 @@
     <t xml:space="preserve">Прибыль после налога</t>
   </si>
   <si>
-    <t xml:space="preserve">Своих денег нужно сверх кредита (максимум)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сколько вложить из своего кармана в самый затратный момент проекта</t>
+    <t xml:space="preserve">Вложено своих денег на пике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сколько денег занято в проекте в самый затратный момент; покупка без кредита</t>
   </si>
   <si>
     <t xml:space="preserve">Прибыль на свои деньги до налога</t>
@@ -345,25 +345,25 @@
     <t xml:space="preserve">Энергия и охрана в простое, € на м² в год</t>
   </si>
   <si>
-    <t xml:space="preserve">Финансирование</t>
+    <t xml:space="preserve">Кредит — по умолчанию не используется: покупка за свои средства</t>
   </si>
   <si>
     <t xml:space="preserve">Кредит, доля цены покупки (LTV)</t>
   </si>
   <si>
-    <t xml:space="preserve">банк под пустое здание даёт 50–60 %</t>
+    <t xml:space="preserve">0 % — покупка за свои средства; можно поставить 50–60 %, чтобы сравнить</t>
   </si>
   <si>
     <t xml:space="preserve">Euribor 3M</t>
   </si>
   <si>
-    <t xml:space="preserve">euribor-rates.eu, 14.10.2026</t>
+    <t xml:space="preserve">только если включить кредит; euribor-rates.eu, 14.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Маржа банка</t>
   </si>
   <si>
-    <t xml:space="preserve">оценка для кредита под пустое здание</t>
+    <t xml:space="preserve">только если включить кредит</t>
   </si>
   <si>
     <t xml:space="preserve">Комиссия банка, % кредита</t>
@@ -576,9 +576,6 @@
     <t xml:space="preserve">Заработок на € 100 затрат</t>
   </si>
   <si>
-    <t xml:space="preserve">Своих денег нужно сверх кредита</t>
-  </si>
-  <si>
     <t xml:space="preserve">В пересчёте на год до налога (IRR)</t>
   </si>
   <si>
@@ -648,7 +645,7 @@
     <t xml:space="preserve">Формулы от листов «Допущения», «Аренда» и «Сводка»</t>
   </si>
   <si>
-    <t xml:space="preserve">Держать сданным и рефинансировать</t>
+    <t xml:space="preserve">Держать сданным</t>
   </si>
   <si>
     <t xml:space="preserve">Расходы владельца, % аренды</t>
@@ -657,7 +654,10 @@
     <t xml:space="preserve">налог OZB владельца, страховка, ремонт, управление</t>
   </si>
   <si>
-    <t xml:space="preserve">Новый кредит, % стоимости со сдачей</t>
+    <t xml:space="preserve">Кредит под сданное здание, % стоимости</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 % — держим без кредита</t>
   </si>
   <si>
     <t xml:space="preserve">Чистый доход в год</t>
@@ -1416,10 +1416,7 @@
     <t xml:space="preserve">VPB 2026: 19 % до € 200.000, 25,8 % сверх (KVK)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ставка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euribor 3M 2,628 % на 14.10.2026 (euribor-rates.eu)</t>
+    <t xml:space="preserve">в модели не используется; Euribor 3M 2,628 % на 14.10.2026 (euribor-rates.eu) — на случай кредита</t>
   </si>
   <si>
     <t xml:space="preserve">Рынок</t>
@@ -2076,7 +2073,7 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">IF(ltv&gt;0,valuation,0)</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2094,7 +2091,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">loan*bank_fee</f>
-        <v>5750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2103,7 +2100,7 @@
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>1301350</v>
+        <v>1292100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2112,7 +2109,7 @@
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">buy_price*ltv</f>
-        <v>575000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2218,7 +2215,7 @@
       </c>
       <c r="B25" s="5" t="n">
         <f aca="false">-(SUM('Денежный поток'!B5:Z9)+SUM('Денежный поток'!B11:Z11)+SUM('Денежный поток'!B14:Z14))</f>
-        <v>1434879.54090909</v>
+        <v>1394706.04090909</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2227,7 +2224,7 @@
       </c>
       <c r="B26" s="7" t="n">
         <f aca="false">SUM('Денежный поток'!B15:Z15)</f>
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2236,7 +2233,7 @@
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">profit/cost_total*100</f>
-        <v>9.77026139276898</v>
+        <v>12.9321144762962</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>28</v>
@@ -2248,7 +2245,7 @@
       </c>
       <c r="B28" s="5" t="n">
         <f aca="false">IF(profit&lt;=0,0,MIN(profit,vpb_step)*vpb_low+MAX(0,profit-vpb_step)*vpb_high)</f>
-        <v>26636.3815454545</v>
+        <v>34269.3465454546</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2257,7 +2254,7 @@
       </c>
       <c r="B29" s="7" t="n">
         <f aca="false">profit-vpb</f>
-        <v>113555.100272727</v>
+        <v>146095.635272727</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2266,7 +2263,7 @@
       </c>
       <c r="B30" s="7" t="n">
         <f aca="false">-MIN('Денежный поток'!B16:Z16)</f>
-        <v>822585.658333334</v>
+        <v>1370296.95</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>32</v>
@@ -2278,7 +2275,7 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">profit/equity</f>
-        <v>0.170427821586664</v>
+        <v>0.131624741497222</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2287,7 +2284,7 @@
       </c>
       <c r="B32" s="10" t="n">
         <f aca="false">(profit-vpb)/equity</f>
-        <v>0.138046535485198</v>
+        <v>0.10661604061275</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2296,7 +2293,7 @@
       </c>
       <c r="B33" s="11" t="n">
         <f aca="false">(1+IRR('Денежный поток'!B15:Z15,0.01))^12-1</f>
-        <v>0.176812251563086</v>
+        <v>0.134101918551975</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>36</v>
@@ -2308,7 +2305,7 @@
       </c>
       <c r="B34" s="10" t="n">
         <f aca="false">(1+IRR('Денежный поток'!B18:Z18,0.01))^12-1</f>
-        <v>0.143189239234856</v>
+        <v>0.108617273669284</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2317,7 +2314,7 @@
       </c>
       <c r="B35" s="9" t="n">
         <f aca="false">(equity+profit-vpb)/equity</f>
-        <v>1.1380465354852</v>
+        <v>1.10661604061275</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>39</v>
@@ -2368,11 +2365,11 @@
         <v>46</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1271706</v>
+        <v>1311040</v>
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">B42/ask-1</f>
-        <v>-0.149360535117057</v>
+        <v>-0.12305016722408</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2380,11 +2377,11 @@
         <v>47</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1147398</v>
+        <v>1183193</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">B43/ask-1</f>
-        <v>-0.232509698996656</v>
+        <v>-0.208566555183947</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2392,11 +2389,11 @@
         <v>48</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>1093352</v>
+        <v>1127608</v>
       </c>
       <c r="C44" s="10" t="n">
         <f aca="false">B44/ask-1</f>
-        <v>-0.268660869565217</v>
+        <v>-0.245747157190635</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2404,11 +2401,11 @@
         <v>49</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>1317315</v>
+        <v>1343282</v>
       </c>
       <c r="C45" s="10" t="n">
         <f aca="false">B45/ask-1</f>
-        <v>-0.118852842809365</v>
+        <v>-0.101483612040134</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2416,11 +2413,11 @@
         <v>50</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>1183788</v>
+        <v>1207360</v>
       </c>
       <c r="C46" s="10" t="n">
         <f aca="false">B46/ask-1</f>
-        <v>-0.20816856187291</v>
+        <v>-0.192401337792642</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2428,7 +2425,7 @@
         <v>51</v>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.0909824223174786</v>
+        <v>0.0937444599911043</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2436,7 +2433,7 @@
         <v>52</v>
       </c>
       <c r="B48" s="9" t="n">
-        <v>56.6309741238001</v>
+        <v>55.0024403582632</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2675,7 +2672,7 @@
         <v>82</v>
       </c>
       <c r="B25" s="16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>83</v>
@@ -2710,7 +2707,9 @@
       <c r="B28" s="16" t="n">
         <v>0.01</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
@@ -3151,7 +3150,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">IF(B$3=0,-acq_total,0)</f>
-        <v>-1301350</v>
+        <v>-1292100</v>
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">IF(C$3=0,-acq_total,0)</f>
@@ -3785,51 +3784,51 @@
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">IF(AND(C$3&gt;=1,C$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">IF(AND(D$3&gt;=1,D$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">IF(AND(E$3&gt;=1,E$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">IF(AND(F$3&gt;=1,F$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">IF(AND(G$3&gt;=1,G$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">IF(AND(H$3&gt;=1,H$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="I11" s="5" t="n">
         <f aca="false">IF(AND(I$3&gt;=1,I$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="J11" s="5" t="n">
         <f aca="false">IF(AND(J$3&gt;=1,J$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="K11" s="5" t="n">
         <f aca="false">IF(AND(K$3&gt;=1,K$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="L11" s="5" t="n">
         <f aca="false">IF(AND(L$3&gt;=1,L$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="M11" s="5" t="n">
         <f aca="false">IF(AND(M$3&gt;=1,M$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="N11" s="5" t="n">
         <f aca="false">IF(AND(N$3&gt;=1,N$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
-        <v>-2576.95833333333</v>
+        <v>-0</v>
       </c>
       <c r="O11" s="5" t="n">
         <f aca="false">IF(AND(O$3&gt;=1,O$3&lt;=sale_month),-loan*loan_rate/12,0)</f>
@@ -3886,7 +3885,7 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">IF(B$3=0,loan,0)-IF(B$3=sale_month,loan,0)</f>
-        <v>575000</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">IF(C$3=0,loan,0)-IF(C$3=sale_month,loan,0)</f>
@@ -3934,7 +3933,7 @@
       </c>
       <c r="N12" s="5" t="n">
         <f aca="false">IF(N$3=0,loan,0)-IF(N$3=sale_month,loan,0)</f>
-        <v>-575000</v>
+        <v>0</v>
       </c>
       <c r="O12" s="5" t="n">
         <f aca="false">IF(O$3=0,loan,0)-IF(O$3=sale_month,loan,0)</f>
@@ -4201,55 +4200,55 @@
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">SUM(B5:B14)</f>
-        <v>-726350</v>
+        <v>-1292100</v>
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">SUM(C5:C14)</f>
-        <v>-29562.0583333333</v>
+        <v>-26985.1</v>
       </c>
       <c r="D15" s="25" t="n">
         <f aca="false">SUM(D5:D14)</f>
-        <v>-29562.0583333333</v>
+        <v>-26985.1</v>
       </c>
       <c r="E15" s="25" t="n">
         <f aca="false">SUM(E5:E14)</f>
-        <v>-3655.95833333333</v>
+        <v>-1079</v>
       </c>
       <c r="F15" s="25" t="n">
         <f aca="false">SUM(F5:F14)</f>
-        <v>-3655.95833333333</v>
+        <v>-1079</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">SUM(G5:G14)</f>
-        <v>-23495.7083333333</v>
+        <v>-20918.75</v>
       </c>
       <c r="H15" s="25" t="n">
         <f aca="false">SUM(H5:H14)</f>
-        <v>-3151.95833333333</v>
+        <v>-575</v>
       </c>
       <c r="I15" s="25" t="n">
         <f aca="false">SUM(I5:I14)</f>
-        <v>-3151.95833333333</v>
+        <v>-575</v>
       </c>
       <c r="J15" s="25" t="n">
         <f aca="false">SUM(J5:J14)</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="K15" s="25" t="n">
         <f aca="false">SUM(K5:K14)</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="L15" s="25" t="n">
         <f aca="false">SUM(L5:L14)</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="M15" s="25" t="n">
         <f aca="false">SUM(M5:M14)</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="N15" s="25" t="n">
         <f aca="false">SUM(N5:N14)</f>
-        <v>933509.973484848</v>
+        <v>1511086.93181818</v>
       </c>
       <c r="O15" s="25" t="n">
         <f aca="false">SUM(O5:O14)</f>
@@ -4306,103 +4305,103 @@
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">B15</f>
-        <v>-726350</v>
+        <v>-1292100</v>
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">B16+C15</f>
-        <v>-755912.058333333</v>
+        <v>-1319085.1</v>
       </c>
       <c r="D16" s="25" t="n">
         <f aca="false">C16+D15</f>
-        <v>-785474.116666667</v>
+        <v>-1346070.2</v>
       </c>
       <c r="E16" s="25" t="n">
         <f aca="false">D16+E15</f>
-        <v>-789130.075</v>
+        <v>-1347149.2</v>
       </c>
       <c r="F16" s="25" t="n">
         <f aca="false">E16+F15</f>
-        <v>-792786.033333333</v>
+        <v>-1348228.2</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">F16+G15</f>
-        <v>-816281.741666667</v>
+        <v>-1369146.95</v>
       </c>
       <c r="H16" s="25" t="n">
         <f aca="false">G16+H15</f>
-        <v>-819433.7</v>
+        <v>-1369721.95</v>
       </c>
       <c r="I16" s="25" t="n">
         <f aca="false">H16+I15</f>
-        <v>-822585.658333334</v>
+        <v>-1370296.95</v>
       </c>
       <c r="J16" s="25" t="n">
         <f aca="false">I16+J15</f>
-        <v>-815268.866666667</v>
+        <v>-1360403.2</v>
       </c>
       <c r="K16" s="25" t="n">
         <f aca="false">J16+K15</f>
-        <v>-807952.075</v>
+        <v>-1350509.45</v>
       </c>
       <c r="L16" s="25" t="n">
         <f aca="false">K16+L15</f>
-        <v>-800635.283333334</v>
+        <v>-1340615.7</v>
       </c>
       <c r="M16" s="25" t="n">
         <f aca="false">L16+M15</f>
-        <v>-793318.491666667</v>
+        <v>-1330721.95</v>
       </c>
       <c r="N16" s="25" t="n">
         <f aca="false">M16+N15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="O16" s="25" t="n">
         <f aca="false">N16+O15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="P16" s="25" t="n">
         <f aca="false">O16+P15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="Q16" s="25" t="n">
         <f aca="false">P16+Q15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="R16" s="25" t="n">
         <f aca="false">Q16+R15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="S16" s="25" t="n">
         <f aca="false">R16+S15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="T16" s="25" t="n">
         <f aca="false">S16+T15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="U16" s="25" t="n">
         <f aca="false">T16+U15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="V16" s="25" t="n">
         <f aca="false">U16+V15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="W16" s="25" t="n">
         <f aca="false">V16+W15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="X16" s="25" t="n">
         <f aca="false">W16+X15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="Y16" s="25" t="n">
         <f aca="false">X16+Y15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
       <c r="Z16" s="25" t="n">
         <f aca="false">Y16+Z15</f>
-        <v>140191.481818181</v>
+        <v>180364.981818182</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4459,7 +4458,7 @@
       </c>
       <c r="N17" s="5" t="n">
         <f aca="false">IF(N$3=sale_month,-vpb,0)</f>
-        <v>-26636.3815454545</v>
+        <v>-34269.3465454546</v>
       </c>
       <c r="O17" s="5" t="n">
         <f aca="false">IF(O$3=sale_month,-vpb,0)</f>
@@ -4516,55 +4515,55 @@
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">B15+B17</f>
-        <v>-726350</v>
+        <v>-1292100</v>
       </c>
       <c r="C18" s="25" t="n">
         <f aca="false">C15+C17</f>
-        <v>-29562.0583333333</v>
+        <v>-26985.1</v>
       </c>
       <c r="D18" s="25" t="n">
         <f aca="false">D15+D17</f>
-        <v>-29562.0583333333</v>
+        <v>-26985.1</v>
       </c>
       <c r="E18" s="25" t="n">
         <f aca="false">E15+E17</f>
-        <v>-3655.95833333333</v>
+        <v>-1079</v>
       </c>
       <c r="F18" s="25" t="n">
         <f aca="false">F15+F17</f>
-        <v>-3655.95833333333</v>
+        <v>-1079</v>
       </c>
       <c r="G18" s="25" t="n">
         <f aca="false">G15+G17</f>
-        <v>-23495.7083333333</v>
+        <v>-20918.75</v>
       </c>
       <c r="H18" s="25" t="n">
         <f aca="false">H15+H17</f>
-        <v>-3151.95833333333</v>
+        <v>-575</v>
       </c>
       <c r="I18" s="25" t="n">
         <f aca="false">I15+I17</f>
-        <v>-3151.95833333333</v>
+        <v>-575</v>
       </c>
       <c r="J18" s="25" t="n">
         <f aca="false">J15+J17</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="K18" s="25" t="n">
         <f aca="false">K15+K17</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="L18" s="25" t="n">
         <f aca="false">L15+L17</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="M18" s="25" t="n">
         <f aca="false">M15+M17</f>
-        <v>7316.79166666667</v>
+        <v>9893.75</v>
       </c>
       <c r="N18" s="25" t="n">
         <f aca="false">N15+N17</f>
-        <v>906873.591939394</v>
+        <v>1476817.58527273</v>
       </c>
       <c r="O18" s="25" t="n">
         <f aca="false">O15+O17</f>
@@ -4961,16 +4960,16 @@
         <v>156</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1440632.075</v>
+        <v>1392727.7</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1434879.54090909</v>
+        <v>1394706.04090909</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1433210.21478495</v>
+        <v>1398190.63145161</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1415636.87424242</v>
+        <v>1390925.12424242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4978,16 +4977,16 @@
         <v>26</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>-146694.575</v>
+        <v>-98790.2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>407432.426344086</v>
+        <v>442452.009677419</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>182194.565151515</v>
+        <v>206906.315151515</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4995,16 +4994,16 @@
         <v>157</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-10.1826536799828</v>
+        <v>-7.09328894657584</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>9.770261392769</v>
+        <v>12.9321144762962</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>28.4279599838899</v>
+        <v>31.6446126675918</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>12.8701483033222</v>
+        <v>14.8754459564607</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5012,33 +5011,33 @@
         <v>30</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>-146694.575</v>
+        <v>-98790.2</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>113555.100272727</v>
+        <v>146095.635272727</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>315914.860347312</v>
+        <v>341899.391180645</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>147577.597772727</v>
+        <v>167124.485842424</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>834821.116666667</v>
+        <v>1372224.575</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>822585.658333334</v>
+        <v>1370296.95</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>817662.116666667</v>
+        <v>1370527.325</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>812121.783333333</v>
+        <v>1367563.95</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5046,55 +5045,55 @@
         <v>34</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>-0.175719770464998</v>
+        <v>-0.071992734862659</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.138046535485198</v>
+        <v>0.10661604061275</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.38636357721352</v>
+        <v>0.249465577915891</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.181718556011389</v>
+        <v>0.122205974969159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>-0.148860183152947</v>
+        <v>-0.0589621234670996</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>0.176812251563293</v>
+        <v>0.134101918551975</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.651009942053495</v>
+        <v>0.40799008940136</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.521319673310886</v>
+        <v>0.332501381635923</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>-0.148860183152947</v>
+        <v>-0.0589621234670996</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.143189239234859</v>
+        <v>0.108617273669284</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.499947603789194</v>
+        <v>0.313235361898811</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.413709159362037</v>
+        <v>0.264833971225986</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5102,28 +5101,28 @@
         <v>3</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="F21" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="G21" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="H21" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="I21" s="19" t="s">
         <v>168</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5137,22 +5136,22 @@
         <v>741.56746031746</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-257210.568181818</v>
+        <v>-206035.018181818</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-14.0377204823742</v>
+        <v>-11.5678131144093</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>-0.253591312223221</v>
+        <v>-0.119028583508714</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-193487.084848485</v>
+        <v>-162411.809848485</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>-10.7042738492903</v>
+        <v>-9.14227002651119</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>-0.349532835340184</v>
+        <v>-0.179239203363856</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5166,22 +5165,22 @@
         <v>694.444444444445</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-147781.018181818</v>
+        <v>-99635.0181818181</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-8.57769644013301</v>
+        <v>-5.94940340262537</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>-0.155026577758742</v>
+        <v>-0.0613251057291401</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-90038.5145586296</v>
+        <v>-60715.5145586296</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>-5.29748846401385</v>
+        <v>-3.63495799386566</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>-0.182473541766482</v>
+        <v>-0.0735235682734282</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5195,22 +5194,22 @@
         <v>669.642857142857</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-90186.5181818181</v>
+        <v>-43635.0181818181</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-5.41576999150437</v>
+        <v>-2.69567278301575</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>-0.0979045459235878</v>
+        <v>-0.0278148617800145</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-35591.8986166008</v>
+        <v>-7191.14861660078</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>-2.16648121664762</v>
+        <v>-0.445426017556465</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>-0.0768782527626826</v>
+        <v>-0.009170831047841</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5224,22 +5223,22 @@
         <v>644.84126984127</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>-32592.0181818181</v>
+        <v>12364.9818181819</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>-2.0272916247044</v>
+        <v>0.791254496654323</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>-0.0366580069387602</v>
+        <v>0.00817342682037681</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>18854.7173254283</v>
+        <v>46333.2173254283</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>1.1887905897274</v>
+        <v>2.97281561676354</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>0.0435119412078031</v>
+        <v>0.0623662840785062</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5253,22 +5252,22 @@
         <v>620.039682539683</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>25002.4818181819</v>
+        <v>68364.9818181819</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>1.61299201669614</v>
+        <v>4.53738021631167</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.0291741528367133</v>
+        <v>0.0469254799285268</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>73301.3332674571</v>
+        <v>99857.5832674571</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>4.79331702241912</v>
+        <v>6.64528158930385</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>0.18120532097497</v>
+        <v>0.142209273322258</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5282,22 +5281,22 @@
         <v>595.238095238095</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>82596.9818181819</v>
+        <v>124364.981818182</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5.53423239226799</v>
+        <v>8.5727210276348</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.100124646517263</v>
+        <v>0.0887727420530664</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>127747.949209486</v>
+        <v>153381.949209486</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>8.67594427707244</v>
+        <v>10.6014283593865</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>0.339239713206038</v>
+        <v>0.231708425290467</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5311,22 +5310,22 @@
         <v>570.436507936508</v>
       </c>
       <c r="D28" s="28" t="n">
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>9.770261392769</v>
+        <v>12.9321144762962</v>
       </c>
       <c r="F28" s="29" t="n">
-        <v>0.176812251563293</v>
+        <v>0.134101918551975</v>
       </c>
       <c r="G28" s="28" t="n">
-        <v>182194.565151515</v>
+        <v>206906.315151515</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>12.8701483033222</v>
+        <v>14.8754459564607</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>0.521319673310886</v>
+        <v>0.332501381635923</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5340,22 +5339,22 @@
         <v>545.634920634921</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>197785.981818182</v>
+        <v>236364.981818182</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>14.3605699578085</v>
+        <v>17.6562273266259</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>0.259959934412725</v>
+        <v>0.183367004238822</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>236641.181093544</v>
+        <v>260430.681093544</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>17.415002463882</v>
+        <v>19.5072486175139</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>0.731996530866204</v>
+        <v>0.446590000718561</v>
       </c>
     </row>
   </sheetData>
@@ -5383,22 +5382,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="31" t="n">
         <v>0.075</v>
@@ -5427,25 +5426,25 @@
         <v>1100000</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>348155.3</v>
+        <v>386734.3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>294798.445161291</v>
+        <v>333377.445161291</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>244776.39375</v>
+        <v>283355.39375</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>197785.981818182</v>
+        <v>236364.981818182</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>153559.711764706</v>
+        <v>192138.711764706</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>111860.657142857</v>
+        <v>150439.657142857</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>72478.2166666668</v>
+        <v>111057.216666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5453,25 +5452,25 @@
         <v>1150000</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>290560.8</v>
+        <v>330734.3</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>237203.945161291</v>
+        <v>277377.445161291</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>187181.89375</v>
+        <v>227355.39375</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>95965.2117647058</v>
+        <v>136138.711764706</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>54266.1571428573</v>
+        <v>94439.6571428573</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>14883.7166666668</v>
+        <v>55057.2166666668</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5479,25 +5478,25 @@
         <v>1200000</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>232966.3</v>
+        <v>274734.3</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>179609.445161291</v>
+        <v>221377.445161291</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>129587.39375</v>
+        <v>171355.39375</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>82596.9818181819</v>
+        <v>124364.981818182</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>38370.7117647058</v>
+        <v>80138.7117647058</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-3328.34285714268</v>
+        <v>38439.6571428573</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-42710.7833333332</v>
+        <v>-942.783333333209</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5505,25 +5504,25 @@
         <v>1250000</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>175371.8</v>
+        <v>218734.3</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>122014.945161291</v>
+        <v>165377.445161291</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>71992.8937500001</v>
+        <v>115355.39375</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>25002.4818181819</v>
+        <v>68364.9818181819</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-19223.7882352942</v>
+        <v>24138.7117647058</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-60922.8428571427</v>
+        <v>-17560.3428571427</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-100305.283333333</v>
+        <v>-56942.7833333332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5531,25 +5530,25 @@
         <v>1300000</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>117777.3</v>
+        <v>162734.3</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>64420.4451612905</v>
+        <v>109377.445161291</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>14398.3937500001</v>
+        <v>59355.3937500001</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-32592.0181818181</v>
+        <v>12364.9818181819</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-76818.2882352942</v>
+        <v>-31861.2882352942</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-118517.342857143</v>
+        <v>-73560.3428571427</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-157899.783333333</v>
+        <v>-112942.783333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5557,25 +5556,25 @@
         <v>1400000</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2588.30000000005</v>
+        <v>50734.3000000001</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-50768.5548387095</v>
+        <v>-2622.55483870953</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-100790.60625</v>
+        <v>-52644.60625</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-147781.018181818</v>
+        <v>-99635.0181818181</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-192007.288235294</v>
+        <v>-143861.288235294</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-233706.342857143</v>
+        <v>-185560.342857143</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-273088.783333333</v>
+        <v>-224942.783333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5583,35 +5582,35 @@
         <v>1495000</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>-106841.25</v>
+        <v>-55665.7</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-160198.10483871</v>
+        <v>-109022.55483871</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-210220.15625</v>
+        <v>-159044.60625</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-257210.568181818</v>
+        <v>-206035.018181818</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-301436.838235294</v>
+        <v>-250261.288235294</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-343135.892857143</v>
+        <v>-291960.342857143</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-382518.333333333</v>
+        <v>-331342.783333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" s="31" t="n">
         <v>0.075</v>
@@ -5640,25 +5639,25 @@
         <v>0.85</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>37426.4250000001</v>
+        <v>77599.9250000001</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-7926.90161290322</v>
+        <v>32246.5983870968</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-50445.6453125</v>
+        <v>-10272.1453125</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-90387.4954545456</v>
+        <v>-50213.9954545456</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-127979.825</v>
+        <v>-87806.325</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-163424.021428571</v>
+        <v>-123250.521428571</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-196899.095833333</v>
+        <v>-156725.595833333</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5666,25 +5665,25 @@
         <v>0.9</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>121804.55</v>
+        <v>161978.05</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>73783.3806451613</v>
+        <v>113956.880645161</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>28763.5343750001</v>
+        <v>68937.0343750001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-13527.8363636364</v>
+        <v>26645.6636363636</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-53331.4794117648</v>
+        <v>-13157.9794117648</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-90860.6285714284</v>
+        <v>-50687.1285714284</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-126304.825</v>
+        <v>-86131.325</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5692,25 +5691,25 @@
         <v>0.95</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>206182.675</v>
+        <v>246356.175</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>155493.662903226</v>
+        <v>195667.162903226</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>107972.7140625</v>
+        <v>148146.2140625</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>63331.8227272725</v>
+        <v>103505.322727273</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>21316.8661764707</v>
+        <v>61490.3661764707</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-18297.2357142854</v>
+        <v>21876.2642857146</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-55710.5541666665</v>
+        <v>-15537.0541666665</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5718,25 +5717,25 @@
         <v>1</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>290560.8</v>
+        <v>330734.3</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>237203.945161291</v>
+        <v>277377.445161291</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>187181.89375</v>
+        <v>227355.39375</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>95965.2117647058</v>
+        <v>136138.711764706</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>54266.1571428573</v>
+        <v>94439.6571428573</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>14883.7166666668</v>
+        <v>55057.2166666668</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,25 +5743,25 @@
         <v>1.05</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>374938.925</v>
+        <v>415112.425</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>318914.227419355</v>
+        <v>359087.727419355</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>266391.0734375</v>
+        <v>306564.5734375</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>217051.140909091</v>
+        <v>257224.640909091</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>170613.557352941</v>
+        <v>210787.057352941</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>126829.55</v>
+        <v>167003.05</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>85477.9875000001</v>
+        <v>125651.4875</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5770,25 +5769,25 @@
         <v>1.1</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>459317.05</v>
+        <v>499490.55</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>400624.509677419</v>
+        <v>440798.009677419</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>345600.253125</v>
+        <v>385773.753125</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>293910.8</v>
+        <v>334084.3</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>245261.902941176</v>
+        <v>285435.402941176</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>199392.942857143</v>
+        <v>239566.442857143</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>156072.258333334</v>
+        <v>196245.758333334</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5796,35 +5795,35 @@
         <v>1.15</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>543695.175</v>
+        <v>583868.675</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>482334.791935484</v>
+        <v>522508.291935484</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>424809.4328125</v>
+        <v>464982.9328125</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>370770.459090909</v>
+        <v>410943.959090909</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>319910.248529412</v>
+        <v>360083.748529412</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>271956.335714286</v>
+        <v>312129.835714286</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>226666.529166667</v>
+        <v>266840.029166667</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B27" s="33" t="n">
         <v>6</v>
@@ -5847,19 +5846,19 @@
         <v>3</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>182194.565151515</v>
+        <v>206906.315151515</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>140186.606818182</v>
+        <v>172629.231818182</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>162136.981818182</v>
+        <v>202310.481818182</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>184087.356818182</v>
+        <v>231991.731818182</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>206037.731818182</v>
+        <v>261672.981818182</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5867,19 +5866,19 @@
         <v>5</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>160249.065151515</v>
+        <v>184960.815151515</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>118241.106818182</v>
+        <v>150683.731818182</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>140191.481818182</v>
+        <v>180364.981818182</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>162141.856818182</v>
+        <v>210046.231818182</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>184092.231818182</v>
+        <v>239727.481818182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5888,16 +5887,16 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="n">
-        <v>96295.6068181819</v>
+        <v>128738.231818182</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>118245.981818182</v>
+        <v>158419.481818182</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>140196.356818182</v>
+        <v>188100.731818182</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>162146.731818182</v>
+        <v>217781.981818182</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5907,23 +5906,23 @@
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5" t="n">
-        <v>96300.4818181819</v>
+        <v>136473.981818182</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>118250.856818182</v>
+        <v>166155.231818182</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>140201.231818182</v>
+        <v>195836.481818182</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="34" t="n">
         <v>0</v>
@@ -5946,19 +5945,19 @@
         <v>26</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>128704.981818182</v>
+        <v>153416.731818182</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>155449.773484848</v>
+        <v>180161.523484848</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>182194.565151515</v>
+        <v>206906.315151515</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>208939.356818182</v>
+        <v>233651.106818182</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>235684.148484848</v>
+        <v>260395.898484848</v>
       </c>
     </row>
   </sheetData>
@@ -6023,38 +6022,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
@@ -6072,7 +6073,7 @@
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">acq_total+capex_total+rent_eff*letting_fee+marketing</f>
-        <v>1373505.95</v>
+        <v>1364255.95</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -6082,7 +6083,7 @@
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">hold_noi/hold_invested</f>
-        <v>0.0800301411144233</v>
+        <v>0.0805727656896054</v>
       </c>
       <c r="C9" s="2"/>
     </row>
@@ -6092,7 +6093,7 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">refi_ltv*value_let</f>
-        <v>837500</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2"/>
     </row>
@@ -6102,7 +6103,7 @@
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">hold_loan*loan_rate</f>
-        <v>45040.75</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -6112,7 +6113,7 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">hold_invested-hold_loan</f>
-        <v>536005.95</v>
+        <v>1364255.95</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -6122,7 +6123,7 @@
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">hold_noi-hold_int</f>
-        <v>64881.125</v>
+        <v>109921.875</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -6132,7 +6133,7 @@
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">hold_cash/hold_eq</f>
-        <v>0.12104553130427</v>
+        <v>0.0805727656896054</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -6207,7 +6208,7 @@
       </c>
       <c r="B22" s="5" t="n">
         <f aca="false">loan*loan_rate*split_months/12</f>
-        <v>25769.5833333333</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -6227,7 +6228,7 @@
       </c>
       <c r="B24" s="5" t="n">
         <f aca="false">acq_total+capex_total+split_cost+split_int+split_hold+split_sale_cost</f>
-        <v>1523993.78333333</v>
+        <v>1488974.2</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -6237,7 +6238,7 @@
       </c>
       <c r="B25" s="5" t="n">
         <f aca="false">split_gross-split_total</f>
-        <v>189606.216666667</v>
+        <v>224625.8</v>
       </c>
       <c r="C25" s="2"/>
     </row>
@@ -6247,7 +6248,7 @@
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">(split_gross-split_total)/split_total</f>
-        <v>0.124414035503448</v>
+        <v>0.150859430606655</v>
       </c>
       <c r="C26" s="2"/>
     </row>
@@ -8331,16 +8332,16 @@
         <v>0.0825</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-257210.568181818</v>
+        <v>-206035.018181818</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>0.149360792087094</v>
+        <v>0.123050058637015</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>0.232509452314799</v>
+        <v>0.208566228484954</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>1147398.36878938</v>
+        <v>1183193.48841499</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,16 +8358,16 @@
         <v>0.0775</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>-371897.732795699</v>
+        <v>-311155.182795699</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0.179865583050465</v>
+        <v>0.154772772978362</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0.259439755349203</v>
+        <v>0.236612677736571</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>1329305.63914818</v>
+        <v>1370280.24346286</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8383,16 +8384,16 @@
         <v>0.0825</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-440272.11</v>
+        <v>-401725</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>0.347786303431009</v>
+        <v>0.32637218900299</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0.412163005278568</v>
+        <v>0.392581902477262</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>646032.857198854</v>
+        <v>667552.489177489</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8409,16 +8410,16 @@
         <v>0.075</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>-280423.783333333</v>
+        <v>-241047.533333333</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>0.216397038940511</v>
+        <v>0.191307566137566</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0.292118003808877</v>
+        <v>0.26918455026455</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>796367.245715013</v>
+        <v>822167.380952381</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8435,16 +8436,16 @@
         <v>0.075</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-126702.75</v>
+        <v>-107417.2</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>0.222213190074705</v>
+        <v>0.193753968253968</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0.299359129672788</v>
+        <v>0.273096500721501</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>346817.23081197</v>
+        <v>359817.232142857</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8461,16 +8462,16 @@
         <v>0.0775</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>-114711.239784946</v>
+        <v>-98774.1397849462</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0.255346764069455</v>
+        <v>0.226131272401434</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0.33081956193202</v>
+        <v>0.303753023410281</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>260980.370846512</v>
+        <v>271536.32086999</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8487,16 +8488,16 @@
         <v>0.0725</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-83391.3534482757</v>
+        <v>-53582.1034482757</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>0.0877518065285335</v>
+        <v>0.0579892894461861</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>0.176245108193014</v>
+        <v>0.14900227985181</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>679597.785740763</v>
+        <v>702073.119122257</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8513,16 +8514,16 @@
         <v>0.0725</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>-121574.191954023</v>
+        <v>-100534.691954023</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0.191896783000939</v>
+        <v>0.163205668756531</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>0.271255292235537</v>
+        <v>0.244823769829961</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>400809.589270455</v>
+        <v>415346.926593522</v>
       </c>
     </row>
   </sheetData>
@@ -8658,42 +8659,42 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="37" t="s">
         <v>438</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="37" t="s">
         <v>440</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B12" s="37" t="s">
         <v>444</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
+++ b/dutch-property-reports/output/Флип-модель Kernweg 1 Хорн (16.10.26).xlsx
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="463">
   <si>
     <t xml:space="preserve">Флип-модель: Kernweg 1, Хорн — сводка</t>
   </si>
@@ -609,10 +609,64 @@
     <t xml:space="preserve">В год, 6 мес.</t>
   </si>
   <si>
-    <t xml:space="preserve">Чувствительность прибыли до налога</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Продажа через 12 месяцев; остальные допущения базовые</t>
+    <t xml:space="preserve">Что будет, если расчёт не сойдётся</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Покупка за € 1.150.000, продажа через 12 месяцев; меняется одно допущение, остальные — как в базовом расчёте</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если инвестор захочет другую доходность (аренда в год / доходность = цена, которую он заплатит)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инвестор хочет получать в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Значит, заплатит за здание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наша прибыль за 12 месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если аренда окажется другой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аренда к нашей оценке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инвестор заплатит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если арендатор въедет позже: прибыль до налога</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Арендатор въезжает</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продаём через 9 месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">через 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">через 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">через 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">на 3-м месяце</t>
+  </si>
+  <si>
+    <t xml:space="preserve">на 5-м месяце</t>
+  </si>
+  <si>
+    <t xml:space="preserve">на 7-м месяце</t>
+  </si>
+  <si>
+    <t xml:space="preserve">на 9-м месяце</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Те же расчёты сеткой: прибыль в евро, когда меняются сразу два допущения</t>
   </si>
   <si>
     <t xml:space="preserve">Прибыль: цена покупки (строки) и доходность, которую требует инвестор (столбцы)</t>
@@ -1441,7 +1495,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;€ &quot;#,##0;[RED]&quot;-€ &quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
@@ -1449,7 +1503,8 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="0.00%"/>
     <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="\+0%;\-0%;0%"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1603,7 +1658,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1728,11 +1783,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1740,7 +1815,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5373,10 +5448,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
@@ -5395,573 +5470,876 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="n">
         <v>0.075</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="B6" s="5" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>330734.3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
         <v>0.0775</v>
       </c>
-      <c r="D5" s="31" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>0.0825</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <v>0.0875</v>
-      </c>
-      <c r="H5" s="31" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>386734.3</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>333377.445161291</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>283355.39375</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>236364.981818182</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>192138.711764706</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>150439.657142857</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>111057.216666667</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="n">
-        <v>1150000</v>
-      </c>
       <c r="B7" s="5" t="n">
-        <v>330734.3</v>
+        <v>1620967.74193548</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>277377.445161291</v>
       </c>
-      <c r="D7" s="5" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1570312.5</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>227355.39375</v>
       </c>
-      <c r="E7" s="5" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1522727.27272727</v>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>180364.981818182</v>
       </c>
-      <c r="F7" s="5" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1477941.17647059</v>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>136138.711764706</v>
       </c>
-      <c r="G7" s="5" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1435714.28571429</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>94439.6571428573</v>
       </c>
-      <c r="H7" s="5" t="n">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1395833.33333333</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>55057.2166666668</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>106781.25</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1294318.18181818</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-50213.9954545456</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>113062.5</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1370454.54545455</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>26645.6636363636</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>119343.75</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1446590.90909091</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>103505.322727273</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>125625</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1522727.27272727</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>180364.981818182</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>131906.25</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1598863.63636364</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>257224.640909091</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>138187.5</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>334084.3</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>144468.75</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1751136.36363636</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>410943.959090909</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>172629.231818182</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>202310.481818182</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>231991.731818182</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>261672.981818182</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>150683.731818182</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>180364.981818182</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>210046.231818182</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>239727.481818182</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>128738.231818182</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>158419.481818182</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>188100.731818182</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>217781.981818182</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5" t="n">
+        <v>136473.981818182</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>166155.231818182</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>195836.481818182</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C34" s="36" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="D34" s="36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E34" s="36" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F34" s="36" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="G34" s="36" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="H34" s="36" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>386734.3</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>333377.445161291</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>283355.39375</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>236364.981818182</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>192138.711764706</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>150439.657142857</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>111057.216666667</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>330734.3</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>277377.445161291</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>227355.39375</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>180364.981818182</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>136138.711764706</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>94439.6571428573</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>55057.2166666668</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="n">
         <v>1200000</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B37" s="5" t="n">
         <v>274734.3</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C37" s="5" t="n">
         <v>221377.445161291</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D37" s="5" t="n">
         <v>171355.39375</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E37" s="5" t="n">
         <v>124364.981818182</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F37" s="5" t="n">
         <v>80138.7117647058</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>38439.6571428573</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H37" s="5" t="n">
         <v>-942.783333333209</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="n">
         <v>1250000</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B38" s="5" t="n">
         <v>218734.3</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C38" s="5" t="n">
         <v>165377.445161291</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D38" s="5" t="n">
         <v>115355.39375</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E38" s="5" t="n">
         <v>68364.9818181819</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>24138.7117647058</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <v>-17560.3428571427</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H38" s="5" t="n">
         <v>-56942.7833333332</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="n">
         <v>1300000</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B39" s="5" t="n">
         <v>162734.3</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C39" s="5" t="n">
         <v>109377.445161291</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D39" s="5" t="n">
         <v>59355.3937500001</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>12364.9818181819</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>-31861.2882352942</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>-73560.3428571427</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H39" s="5" t="n">
         <v>-112942.783333333</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="n">
         <v>1400000</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B40" s="5" t="n">
         <v>50734.3000000001</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C40" s="5" t="n">
         <v>-2622.55483870953</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D40" s="5" t="n">
         <v>-52644.60625</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E40" s="5" t="n">
         <v>-99635.0181818181</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F40" s="5" t="n">
         <v>-143861.288235294</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G40" s="5" t="n">
         <v>-185560.342857143</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H40" s="5" t="n">
         <v>-224942.783333333</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="n">
         <v>1495000</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B41" s="5" t="n">
         <v>-55665.7</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C41" s="5" t="n">
         <v>-109022.55483871</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D41" s="5" t="n">
         <v>-159044.60625</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E41" s="5" t="n">
         <v>-206035.018181818</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F41" s="5" t="n">
         <v>-250261.288235294</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G41" s="5" t="n">
         <v>-291960.342857143</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H41" s="5" t="n">
         <v>-331342.783333333</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16" s="31" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B45" s="36" t="n">
         <v>0.075</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C45" s="36" t="n">
         <v>0.0775</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D45" s="36" t="n">
         <v>0.08</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E45" s="36" t="n">
         <v>0.0825</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F45" s="36" t="n">
         <v>0.085</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G45" s="36" t="n">
         <v>0.0875</v>
       </c>
-      <c r="H16" s="31" t="n">
+      <c r="H45" s="36" t="n">
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="37" t="n">
         <v>0.85</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B46" s="5" t="n">
         <v>77599.9250000001</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C46" s="5" t="n">
         <v>32246.5983870968</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D46" s="5" t="n">
         <v>-10272.1453125</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E46" s="5" t="n">
         <v>-50213.9954545456</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F46" s="5" t="n">
         <v>-87806.325</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G46" s="5" t="n">
         <v>-123250.521428571</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H46" s="5" t="n">
         <v>-156725.595833333</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="37" t="n">
         <v>0.9</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B47" s="5" t="n">
         <v>161978.05</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C47" s="5" t="n">
         <v>113956.880645161</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D47" s="5" t="n">
         <v>68937.0343750001</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E47" s="5" t="n">
         <v>26645.6636363636</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F47" s="5" t="n">
         <v>-13157.9794117648</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G47" s="5" t="n">
         <v>-50687.1285714284</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H47" s="5" t="n">
         <v>-86131.325</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="37" t="n">
         <v>0.95</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B48" s="5" t="n">
         <v>246356.175</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C48" s="5" t="n">
         <v>195667.162903226</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D48" s="5" t="n">
         <v>148146.2140625</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E48" s="5" t="n">
         <v>103505.322727273</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F48" s="5" t="n">
         <v>61490.3661764707</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G48" s="5" t="n">
         <v>21876.2642857146</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H48" s="5" t="n">
         <v>-15537.0541666665</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B49" s="5" t="n">
         <v>330734.3</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C49" s="5" t="n">
         <v>277377.445161291</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D49" s="5" t="n">
         <v>227355.39375</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>180364.981818182</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F49" s="5" t="n">
         <v>136138.711764706</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G49" s="5" t="n">
         <v>94439.6571428573</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H49" s="5" t="n">
         <v>55057.2166666668</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="37" t="n">
         <v>1.05</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B50" s="5" t="n">
         <v>415112.425</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C50" s="5" t="n">
         <v>359087.727419355</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D50" s="5" t="n">
         <v>306564.5734375</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E50" s="5" t="n">
         <v>257224.640909091</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F50" s="5" t="n">
         <v>210787.057352941</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G50" s="5" t="n">
         <v>167003.05</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H50" s="5" t="n">
         <v>125651.4875</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="37" t="n">
         <v>1.1</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B51" s="5" t="n">
         <v>499490.55</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C51" s="5" t="n">
         <v>440798.009677419</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D51" s="5" t="n">
         <v>385773.753125</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E51" s="5" t="n">
         <v>334084.3</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F51" s="5" t="n">
         <v>285435.402941176</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G51" s="5" t="n">
         <v>239566.442857143</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H51" s="5" t="n">
         <v>196245.758333334</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="37" t="n">
         <v>1.15</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B52" s="5" t="n">
         <v>583868.675</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C52" s="5" t="n">
         <v>522508.291935484</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D52" s="5" t="n">
         <v>464982.9328125</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>410943.959090909</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F52" s="5" t="n">
         <v>360083.748529412</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <v>312129.835714286</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H52" s="5" t="n">
         <v>266840.029166667</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" s="33" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B56" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C56" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D56" s="38" t="n">
         <v>12</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E56" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="F27" s="33" t="n">
+      <c r="F56" s="38" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B57" s="5" t="n">
         <v>206906.315151515</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C57" s="5" t="n">
         <v>172629.231818182</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D57" s="5" t="n">
         <v>202310.481818182</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E57" s="5" t="n">
         <v>231991.731818182</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F57" s="5" t="n">
         <v>261672.981818182</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B58" s="5" t="n">
         <v>184960.815151515</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C58" s="5" t="n">
         <v>150683.731818182</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D58" s="5" t="n">
         <v>180364.981818182</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E58" s="5" t="n">
         <v>210046.231818182</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F58" s="5" t="n">
         <v>239727.481818182</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5" t="n">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5" t="n">
         <v>128738.231818182</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D59" s="5" t="n">
         <v>158419.481818182</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>188100.731818182</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F59" s="5" t="n">
         <v>217781.981818182</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="n">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5" t="n">
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5" t="n">
         <v>136473.981818182</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E60" s="5" t="n">
         <v>166155.231818182</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F60" s="5" t="n">
         <v>195836.481818182</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="B35" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="34" t="n">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="39" t="n">
         <v>0.25</v>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D64" s="39" t="n">
         <v>0.5</v>
       </c>
-      <c r="E35" s="34" t="n">
+      <c r="E64" s="39" t="n">
         <v>0.75</v>
       </c>
-      <c r="F35" s="34" t="n">
+      <c r="F64" s="39" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B65" s="5" t="n">
         <v>153416.731818182</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>180161.523484848</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D65" s="5" t="n">
         <v>206906.315151515</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>233651.106818182</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>260395.898484848</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:H12">
+  <conditionalFormatting sqref="B35:H41">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -5973,7 +6351,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17:H23">
+  <conditionalFormatting sqref="B46:H52">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -5985,7 +6363,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F31">
+  <conditionalFormatting sqref="B57:F60">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -6022,44 +6400,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>0.125</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">rent_eff*(1-hold_opex)</f>
@@ -6069,7 +6447,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">acq_total+capex_total+rent_eff*letting_fee+marketing</f>
@@ -6079,7 +6457,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B9" s="12" t="n">
         <f aca="false">hold_noi/hold_invested</f>
@@ -6089,7 +6467,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">refi_ltv*value_let</f>
@@ -6099,7 +6477,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">hold_loan*loan_rate</f>
@@ -6109,7 +6487,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">hold_invested-hold_loan</f>
@@ -6119,7 +6497,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B13" s="5" t="n">
         <f aca="false">hold_noi-hold_int</f>
@@ -6129,7 +6507,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">hold_cash/hold_eq</f>
@@ -6139,23 +6517,23 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B16" s="14" t="n">
         <v>850</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>90000</v>
@@ -6166,7 +6544,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B18" s="15" t="n">
         <v>10</v>
@@ -6175,7 +6553,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>0.02</v>
@@ -6184,7 +6562,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">split_pm2*area_vvo</f>
@@ -6194,7 +6572,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B21" s="5" t="n">
         <f aca="false">split_gross*split_fee+2*5000</f>
@@ -6204,7 +6582,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B22" s="5" t="n">
         <f aca="false">loan*loan_rate*split_months/12</f>
@@ -6214,7 +6592,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B23" s="5" t="n">
         <f aca="false">(buy_price*holding_pct+void_m2*area_vvo)*split_months/12</f>
@@ -6244,7 +6622,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">(split_gross-split_total)/split_total</f>
@@ -6283,54 +6661,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>11195</v>
@@ -6341,25 +6719,25 @@
       <c r="E6" s="5" t="n">
         <v>509</v>
       </c>
-      <c r="F6" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>222</v>
+      <c r="F6" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1737</v>
@@ -6370,25 +6748,25 @@
       <c r="E7" s="5" t="n">
         <v>518</v>
       </c>
-      <c r="F7" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>226</v>
+      <c r="F7" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>11289</v>
@@ -6399,25 +6777,25 @@
       <c r="E8" s="5" t="n">
         <v>576</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>228</v>
+      <c r="F8" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>4220</v>
@@ -6428,25 +6806,25 @@
       <c r="E9" s="5" t="n">
         <v>662</v>
       </c>
-      <c r="F9" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>231</v>
+      <c r="F9" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>2155</v>
@@ -6457,25 +6835,25 @@
       <c r="E10" s="5" t="n">
         <v>694</v>
       </c>
-      <c r="F10" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>234</v>
+      <c r="F10" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>694</v>
@@ -6486,25 +6864,25 @@
       <c r="E11" s="5" t="n">
         <v>829</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I11" s="36" t="s">
+      <c r="F11" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" s="40" t="s">
         <v>238</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>4500</v>
@@ -6515,25 +6893,25 @@
       <c r="E12" s="5" t="n">
         <v>833</v>
       </c>
-      <c r="F12" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>241</v>
+      <c r="F12" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H12" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>1625</v>
@@ -6544,25 +6922,25 @@
       <c r="E13" s="5" t="n">
         <v>922</v>
       </c>
-      <c r="F13" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>243</v>
+      <c r="F13" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H13" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>936</v>
@@ -6573,25 +6951,25 @@
       <c r="E14" s="5" t="n">
         <v>935</v>
       </c>
-      <c r="F14" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>248</v>
+      <c r="F14" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H14" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>1100</v>
@@ -6602,25 +6980,25 @@
       <c r="E15" s="5" t="n">
         <v>999</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>249</v>
+      <c r="F15" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H15" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>11976</v>
@@ -6631,25 +7009,25 @@
       <c r="E16" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="F16" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>251</v>
+      <c r="F16" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>2258</v>
@@ -6660,25 +7038,25 @@
       <c r="E17" s="5" t="n">
         <v>1041</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>256</v>
+      <c r="F17" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>3000</v>
@@ -6689,25 +7067,25 @@
       <c r="E18" s="5" t="n">
         <v>1083</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>259</v>
+      <c r="F18" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>528</v>
@@ -6718,25 +7096,25 @@
       <c r="E19" s="5" t="n">
         <v>1127</v>
       </c>
-      <c r="F19" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I19" s="36" t="s">
-        <v>264</v>
+      <c r="F19" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>1628</v>
@@ -6747,25 +7125,25 @@
       <c r="E20" s="5" t="n">
         <v>1161</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>267</v>
+      <c r="F20" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>462</v>
@@ -6776,25 +7154,25 @@
       <c r="E21" s="5" t="n">
         <v>1180</v>
       </c>
-      <c r="F21" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="I21" s="36" t="s">
-        <v>272</v>
+      <c r="F21" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>471</v>
@@ -6805,25 +7183,25 @@
       <c r="E22" s="5" t="n">
         <v>1258</v>
       </c>
-      <c r="F22" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>274</v>
+      <c r="F22" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>446</v>
@@ -6834,25 +7212,25 @@
       <c r="E23" s="5" t="n">
         <v>1289</v>
       </c>
-      <c r="F23" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>277</v>
+      <c r="F23" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>869</v>
@@ -6863,25 +7241,25 @@
       <c r="E24" s="5" t="n">
         <v>1375</v>
       </c>
-      <c r="F24" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>280</v>
+      <c r="F24" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>563</v>
@@ -6892,25 +7270,25 @@
       <c r="E25" s="5" t="n">
         <v>1465</v>
       </c>
-      <c r="F25" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" s="36" t="s">
-        <v>283</v>
+      <c r="F25" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>400</v>
@@ -6921,25 +7299,25 @@
       <c r="E26" s="5" t="n">
         <v>1480</v>
       </c>
-      <c r="F26" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>286</v>
+      <c r="F26" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>1248</v>
@@ -6950,25 +7328,25 @@
       <c r="E27" s="5" t="n">
         <v>1482</v>
       </c>
-      <c r="F27" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>289</v>
+      <c r="F27" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="G27" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>669</v>
@@ -6979,25 +7357,25 @@
       <c r="E28" s="5" t="n">
         <v>1487</v>
       </c>
-      <c r="F28" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="G28" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="I28" s="36" t="s">
-        <v>292</v>
+      <c r="F28" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="G28" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>635</v>
@@ -7008,25 +7386,25 @@
       <c r="E29" s="5" t="n">
         <v>1535</v>
       </c>
-      <c r="F29" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="G29" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>296</v>
+      <c r="F29" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="G29" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>900</v>
@@ -7037,25 +7415,25 @@
       <c r="E30" s="5" t="n">
         <v>1556</v>
       </c>
-      <c r="F30" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="G30" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I30" s="36" t="s">
-        <v>299</v>
+      <c r="F30" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="G30" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>725</v>
@@ -7066,25 +7444,25 @@
       <c r="E31" s="5" t="n">
         <v>1586</v>
       </c>
-      <c r="F31" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="G31" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I31" s="36" t="s">
-        <v>300</v>
+      <c r="F31" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="G31" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>1205</v>
@@ -7095,25 +7473,25 @@
       <c r="E32" s="5" t="n">
         <v>1618</v>
       </c>
-      <c r="F32" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="I32" s="36" t="s">
-        <v>303</v>
+      <c r="F32" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="I32" s="41" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>774</v>
@@ -7124,25 +7502,25 @@
       <c r="E33" s="5" t="n">
         <v>1738</v>
       </c>
-      <c r="F33" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="G33" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H33" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I33" s="36" t="s">
-        <v>305</v>
+      <c r="F33" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H33" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>762</v>
@@ -7153,25 +7531,25 @@
       <c r="E34" s="5" t="n">
         <v>1739</v>
       </c>
-      <c r="F34" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I34" s="36" t="s">
-        <v>308</v>
+      <c r="F34" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>460</v>
@@ -7182,57 +7560,57 @@
       <c r="E35" s="5" t="n">
         <v>1739</v>
       </c>
-      <c r="F35" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="G35" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H35" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>309</v>
+      <c r="F35" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="G35" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>131</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G38" s="19"/>
       <c r="H38" s="19" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>12137</v>
@@ -7243,22 +7621,22 @@
       <c r="E39" s="5" t="n">
         <v>599567.8</v>
       </c>
-      <c r="F39" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>314</v>
+      <c r="F39" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>8583</v>
@@ -7269,22 +7647,22 @@
       <c r="E40" s="5" t="n">
         <v>750154.2</v>
       </c>
-      <c r="F40" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>317</v>
+      <c r="F40" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="H40" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>5180</v>
@@ -7295,22 +7673,22 @@
       <c r="E41" s="5" t="n">
         <v>294224</v>
       </c>
-      <c r="F41" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>318</v>
+      <c r="F41" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="H41" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>4676</v>
@@ -7321,22 +7699,22 @@
       <c r="E42" s="5" t="n">
         <v>288041.6</v>
       </c>
-      <c r="F42" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I42" s="36" t="s">
-        <v>321</v>
+      <c r="F42" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>2900</v>
@@ -7347,22 +7725,22 @@
       <c r="E43" s="5" t="n">
         <v>174000</v>
       </c>
-      <c r="F43" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="H43" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="I43" s="36" t="s">
-        <v>323</v>
+      <c r="F43" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="H43" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>2710</v>
@@ -7373,22 +7751,22 @@
       <c r="E44" s="5" t="n">
         <v>204063</v>
       </c>
-      <c r="F44" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="H44" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="I44" s="36" t="s">
-        <v>325</v>
+      <c r="F44" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>320</v>
+      </c>
+      <c r="I44" s="41" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>2695</v>
@@ -7399,22 +7777,22 @@
       <c r="E45" s="5" t="n">
         <v>188919.5</v>
       </c>
-      <c r="F45" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="H45" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I45" s="36" t="s">
-        <v>328</v>
+      <c r="F45" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="H45" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I45" s="41" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>1776</v>
@@ -7425,22 +7803,22 @@
       <c r="E46" s="5" t="n">
         <v>114019.2</v>
       </c>
-      <c r="F46" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="I46" s="36" t="s">
-        <v>329</v>
+      <c r="F46" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="I46" s="41" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>1713</v>
@@ -7451,22 +7829,22 @@
       <c r="E47" s="5" t="n">
         <v>98326.2</v>
       </c>
-      <c r="F47" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>332</v>
+      <c r="F47" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="H47" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1485</v>
@@ -7477,22 +7855,22 @@
       <c r="E48" s="5" t="n">
         <v>111523.5</v>
       </c>
-      <c r="F48" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I48" s="36" t="s">
-        <v>335</v>
+      <c r="F48" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="H48" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I48" s="41" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>1413</v>
@@ -7503,22 +7881,22 @@
       <c r="E49" s="5" t="n">
         <v>111061.8</v>
       </c>
-      <c r="F49" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I49" s="36" t="s">
-        <v>338</v>
+      <c r="F49" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="H49" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>1308</v>
@@ -7529,22 +7907,22 @@
       <c r="E50" s="5" t="n">
         <v>108040.8</v>
       </c>
-      <c r="F50" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="H50" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="I50" s="36" t="s">
-        <v>341</v>
+      <c r="F50" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="H50" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>1278</v>
@@ -7555,22 +7933,22 @@
       <c r="E51" s="5" t="n">
         <v>72590.4</v>
       </c>
-      <c r="F51" s="35" t="s">
-        <v>343</v>
-      </c>
-      <c r="H51" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="I51" s="36" t="s">
-        <v>344</v>
+      <c r="F51" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="H51" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C52" s="8" t="n">
         <v>1248</v>
@@ -7581,22 +7959,22 @@
       <c r="E52" s="5" t="n">
         <v>147513.6</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I52" s="36" t="s">
-        <v>345</v>
+      <c r="F52" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="H52" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I52" s="41" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C53" s="8" t="n">
         <v>976</v>
@@ -7607,22 +7985,22 @@
       <c r="E53" s="5" t="n">
         <v>150011.2</v>
       </c>
-      <c r="F53" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="H53" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I53" s="36" t="s">
-        <v>347</v>
+      <c r="F53" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="H53" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I53" s="41" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C54" s="8" t="n">
         <v>850</v>
@@ -7633,22 +8011,22 @@
       <c r="E54" s="5" t="n">
         <v>71995</v>
       </c>
-      <c r="F54" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="H54" s="35" t="s">
-        <v>348</v>
-      </c>
-      <c r="I54" s="36" t="s">
-        <v>349</v>
+      <c r="F54" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="H54" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>762</v>
@@ -7659,22 +8037,22 @@
       <c r="E55" s="5" t="n">
         <v>83362.8</v>
       </c>
-      <c r="F55" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="H55" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="I55" s="36" t="s">
-        <v>350</v>
+      <c r="F55" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="H55" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C56" s="8" t="n">
         <v>531</v>
@@ -7685,22 +8063,22 @@
       <c r="E56" s="5" t="n">
         <v>30904.2</v>
       </c>
-      <c r="F56" s="35" t="s">
-        <v>353</v>
-      </c>
-      <c r="H56" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>354</v>
+      <c r="F56" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="H56" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I56" s="41" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C57" s="8" t="n">
         <v>482</v>
@@ -7711,22 +8089,22 @@
       <c r="E57" s="5" t="n">
         <v>54996.2</v>
       </c>
-      <c r="F57" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="H57" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I57" s="36" t="s">
-        <v>357</v>
+      <c r="F57" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="H57" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I57" s="41" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C58" s="8" t="n">
         <v>450</v>
@@ -7737,22 +8115,22 @@
       <c r="E58" s="5" t="n">
         <v>64980</v>
       </c>
-      <c r="F58" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I58" s="36" t="s">
-        <v>360</v>
+      <c r="F58" s="40" t="s">
+        <v>377</v>
+      </c>
+      <c r="H58" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I58" s="41" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>438</v>
@@ -7763,22 +8141,22 @@
       <c r="E59" s="5" t="n">
         <v>43362</v>
       </c>
-      <c r="F59" s="35" t="s">
-        <v>362</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>363</v>
-      </c>
-      <c r="I59" s="36" t="s">
-        <v>364</v>
+      <c r="F59" s="40" t="s">
+        <v>380</v>
+      </c>
+      <c r="H59" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C60" s="8" t="n">
         <v>366</v>
@@ -7789,22 +8167,22 @@
       <c r="E60" s="5" t="n">
         <v>34733.4</v>
       </c>
-      <c r="F60" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I60" s="36" t="s">
-        <v>366</v>
+      <c r="F60" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="H60" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I60" s="41" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>365</v>
@@ -7815,22 +8193,22 @@
       <c r="E61" s="5" t="n">
         <v>25805.5</v>
       </c>
-      <c r="F61" s="35" t="s">
-        <v>368</v>
-      </c>
-      <c r="H61" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I61" s="36" t="s">
-        <v>369</v>
+      <c r="F61" s="40" t="s">
+        <v>386</v>
+      </c>
+      <c r="H61" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I61" s="41" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C62" s="8" t="n">
         <v>344</v>
@@ -7841,22 +8219,22 @@
       <c r="E62" s="5" t="n">
         <v>34193.6</v>
       </c>
-      <c r="F62" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="H62" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I62" s="36" t="s">
-        <v>371</v>
+      <c r="F62" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="H62" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I62" s="41" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C63" s="8" t="n">
         <v>342</v>
@@ -7867,22 +8245,22 @@
       <c r="E63" s="5" t="n">
         <v>28215</v>
       </c>
-      <c r="F63" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="H63" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="I63" s="36" t="s">
-        <v>375</v>
+      <c r="F63" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="H63" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C64" s="8" t="n">
         <v>336</v>
@@ -7893,22 +8271,22 @@
       <c r="E64" s="5" t="n">
         <v>21537.6</v>
       </c>
-      <c r="F64" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="H64" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I64" s="36" t="s">
+      <c r="F64" s="40" t="s">
         <v>377</v>
+      </c>
+      <c r="H64" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I64" s="41" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C65" s="8" t="n">
         <v>335</v>
@@ -7919,22 +8297,22 @@
       <c r="E65" s="5" t="n">
         <v>31992.5</v>
       </c>
-      <c r="F65" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="H65" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I65" s="36" t="s">
-        <v>379</v>
+      <c r="F65" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="H65" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I65" s="41" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C66" s="8" t="n">
         <v>333</v>
@@ -7945,22 +8323,22 @@
       <c r="E66" s="5" t="n">
         <v>28205.1</v>
       </c>
-      <c r="F66" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="H66" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I66" s="36" t="s">
-        <v>381</v>
+      <c r="F66" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="H66" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I66" s="41" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>330</v>
@@ -7971,22 +8349,22 @@
       <c r="E67" s="5" t="n">
         <v>25014</v>
       </c>
-      <c r="F67" s="35" t="s">
-        <v>383</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I67" s="36" t="s">
-        <v>384</v>
+      <c r="F67" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="H67" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C68" s="8" t="n">
         <v>325</v>
@@ -7997,22 +8375,22 @@
       <c r="E68" s="5" t="n">
         <v>27007.5</v>
       </c>
-      <c r="F68" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>363</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>386</v>
+      <c r="F68" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="H68" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="I68" s="41" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C69" s="8" t="n">
         <v>311</v>
@@ -8023,22 +8401,22 @@
       <c r="E69" s="5" t="n">
         <v>59991.9</v>
       </c>
-      <c r="F69" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="H69" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I69" s="36" t="s">
-        <v>389</v>
+      <c r="F69" s="40" t="s">
+        <v>406</v>
+      </c>
+      <c r="H69" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I69" s="41" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C70" s="8" t="n">
         <v>310</v>
@@ -8049,22 +8427,22 @@
       <c r="E70" s="5" t="n">
         <v>30225</v>
       </c>
-      <c r="F70" s="35" t="s">
-        <v>391</v>
-      </c>
-      <c r="H70" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I70" s="36" t="s">
-        <v>392</v>
+      <c r="F70" s="40" t="s">
+        <v>409</v>
+      </c>
+      <c r="H70" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I70" s="41" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C71" s="8" t="n">
         <v>304</v>
@@ -8075,22 +8453,22 @@
       <c r="E71" s="5" t="n">
         <v>34230.4</v>
       </c>
-      <c r="F71" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="H71" s="35" t="s">
-        <v>363</v>
-      </c>
-      <c r="I71" s="36" t="s">
-        <v>394</v>
+      <c r="F71" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="H71" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="I71" s="41" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C72" s="8" t="n">
         <v>300</v>
@@ -8101,22 +8479,22 @@
       <c r="E72" s="5" t="n">
         <v>32400</v>
       </c>
-      <c r="F72" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="H72" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I72" s="36" t="s">
-        <v>396</v>
+      <c r="F72" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="H72" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C73" s="8" t="n">
         <v>300</v>
@@ -8127,56 +8505,56 @@
       <c r="E73" s="5" t="n">
         <v>23400</v>
       </c>
-      <c r="F73" s="35" t="s">
-        <v>398</v>
-      </c>
-      <c r="H73" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="I73" s="36" t="s">
-        <v>399</v>
+      <c r="F73" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="H73" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="I73" s="41" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>132</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C77" s="8" t="n">
         <v>188</v>
@@ -8190,22 +8568,22 @@
       <c r="F77" s="12" t="n">
         <v>0.0833</v>
       </c>
-      <c r="G77" s="35" t="s">
-        <v>403</v>
-      </c>
-      <c r="H77" s="35" t="s">
-        <v>404</v>
-      </c>
-      <c r="I77" s="36" t="s">
-        <v>405</v>
+      <c r="G77" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="H77" s="40" t="s">
+        <v>422</v>
+      </c>
+      <c r="I77" s="41" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>583</v>
@@ -8219,22 +8597,22 @@
       <c r="F78" s="12" t="n">
         <v>0.0889</v>
       </c>
-      <c r="G78" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="H78" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I78" s="36" t="s">
-        <v>408</v>
+      <c r="G78" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="H78" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I78" s="41" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>190</v>
@@ -8248,22 +8626,22 @@
       <c r="F79" s="12" t="n">
         <v>0.0935</v>
       </c>
-      <c r="G79" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="H79" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I79" s="36" t="s">
-        <v>410</v>
+      <c r="G79" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="H79" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="I79" s="41" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>2117</v>
@@ -8277,50 +8655,50 @@
       <c r="F80" s="12" t="n">
         <v>0.0855</v>
       </c>
-      <c r="G80" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="H80" s="35" t="s">
-        <v>413</v>
-      </c>
-      <c r="I80" s="36" t="s">
-        <v>414</v>
+      <c r="G80" s="40" t="s">
+        <v>430</v>
+      </c>
+      <c r="H80" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="I80" s="41" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D83" s="19" t="s">
         <v>154</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="B84" s="5" t="n">
         <v>1495000</v>
@@ -8346,7 +8724,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>1795000</v>
@@ -8372,7 +8750,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>1099000</v>
@@ -8398,7 +8776,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>1125000</v>
@@ -8424,7 +8802,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B88" s="5" t="n">
         <v>495000</v>
@@ -8450,7 +8828,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>390000</v>
@@ -8476,7 +8854,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>825000</v>
@@ -8502,7 +8880,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>550000</v>
@@ -8622,79 +9000,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>432</v>
+        <v>434</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>434</v>
+        <v>451</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>436</v>
+        <v>453</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>437</v>
+      <c r="B7" s="42" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="37" t="s">
-        <v>438</v>
+      <c r="B8" s="42" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>440</v>
+        <v>457</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>441</v>
+        <v>457</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>442</v>
+        <v>457</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>444</v>
+        <v>461</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
